--- a/Mixed/1_zhouyf.xlsx
+++ b/Mixed/1_zhouyf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\Mixed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{730F1926-CE03-4126-A295-0CC478FF73C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6C56FF3-97C7-42F9-BC3C-6878BAD04C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22740" yWindow="3990" windowWidth="20880" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17520" yWindow="1005" windowWidth="20880" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="74">
   <si>
     <t>Fre</t>
   </si>
@@ -292,6 +292,154 @@
   </si>
   <si>
     <t>"刚…就…"一般不接人的意志，此处是例外</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>～以上(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>既然…就…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>～上(に)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不仅…而且…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>～</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>おかげで</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)托…的福(2)都怪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>～上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>で</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">(は) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-&gt; 在…方面</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>～上で</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在…之后</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>～あいだに</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在…期间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~ちゃんと</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>牢牢地；好好地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ちょっと-&gt;稍微；一会儿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>やさしい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>容易的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>～ているうちに</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在…过程中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夢中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>着迷；入迷；沉醉</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -387,7 +535,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -399,6 +547,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -732,7 +883,9 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A2" s="3"/>
+      <c r="A2" s="3">
+        <v>0</v>
+      </c>
       <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
@@ -747,7 +900,9 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A3" s="3"/>
+      <c r="A3" s="3">
+        <v>0</v>
+      </c>
       <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
@@ -758,7 +913,9 @@
       <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A4" s="3"/>
+      <c r="A4" s="3">
+        <v>0</v>
+      </c>
       <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
@@ -771,7 +928,9 @@
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A5" s="3"/>
+      <c r="A5" s="3">
+        <v>0</v>
+      </c>
       <c r="B5" s="3" t="s">
         <v>14</v>
       </c>
@@ -786,7 +945,9 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A6" s="3"/>
+      <c r="A6" s="3">
+        <v>0</v>
+      </c>
       <c r="B6" s="3" t="s">
         <v>18</v>
       </c>
@@ -799,7 +960,9 @@
       <c r="E6" s="3"/>
     </row>
     <row r="7" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A7" s="3"/>
+      <c r="A7" s="3">
+        <v>0</v>
+      </c>
       <c r="B7" s="3" t="s">
         <v>21</v>
       </c>
@@ -810,7 +973,9 @@
       <c r="E7" s="3"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A8" s="3"/>
+      <c r="A8" s="3">
+        <v>0</v>
+      </c>
       <c r="B8" s="3" t="s">
         <v>23</v>
       </c>
@@ -823,7 +988,9 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A9" s="3"/>
+      <c r="A9" s="3">
+        <v>0</v>
+      </c>
       <c r="B9" s="3" t="s">
         <v>25</v>
       </c>
@@ -834,7 +1001,9 @@
       <c r="E9" s="3"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A10" s="3"/>
+      <c r="A10" s="3">
+        <v>0</v>
+      </c>
       <c r="B10" s="3" t="s">
         <v>27</v>
       </c>
@@ -845,7 +1014,9 @@
       <c r="E10" s="3"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A11" s="3"/>
+      <c r="A11" s="3">
+        <v>0</v>
+      </c>
       <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
@@ -858,7 +1029,9 @@
       <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A12" s="3"/>
+      <c r="A12" s="3">
+        <v>0</v>
+      </c>
       <c r="B12" s="3" t="s">
         <v>32</v>
       </c>
@@ -871,7 +1044,9 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A13" s="3"/>
+      <c r="A13" s="3">
+        <v>0</v>
+      </c>
       <c r="B13" s="3" t="s">
         <v>36</v>
       </c>
@@ -882,7 +1057,9 @@
       <c r="E13" s="3"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A14" s="3"/>
+      <c r="A14" s="3">
+        <v>0</v>
+      </c>
       <c r="B14" s="3" t="s">
         <v>38</v>
       </c>
@@ -893,7 +1070,9 @@
       <c r="E14" s="3"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A15" s="3"/>
+      <c r="A15" s="3">
+        <v>0</v>
+      </c>
       <c r="B15" s="3" t="s">
         <v>40</v>
       </c>
@@ -906,7 +1085,9 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A16" s="3"/>
+      <c r="A16" s="3">
+        <v>0</v>
+      </c>
       <c r="B16" s="3" t="s">
         <v>43</v>
       </c>
@@ -917,7 +1098,9 @@
       <c r="E16" s="3"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A17" s="3"/>
+      <c r="A17" s="3">
+        <v>0</v>
+      </c>
       <c r="B17" s="3" t="s">
         <v>45</v>
       </c>
@@ -928,7 +1111,9 @@
       <c r="E17" s="3"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A18" s="3"/>
+      <c r="A18" s="3">
+        <v>0</v>
+      </c>
       <c r="B18" s="3" t="s">
         <v>47</v>
       </c>
@@ -938,8 +1123,10 @@
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
     </row>
-    <row r="19" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A19" s="3"/>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A19" s="3">
+        <v>0</v>
+      </c>
       <c r="B19" s="3" t="s">
         <v>48</v>
       </c>
@@ -952,7 +1139,9 @@
       </c>
     </row>
     <row r="20" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A20" s="3"/>
+      <c r="A20" s="3">
+        <v>0</v>
+      </c>
       <c r="B20" s="3" t="s">
         <v>51</v>
       </c>
@@ -964,66 +1153,110 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
+    <row r="21" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A21" s="3">
+        <v>0</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>55</v>
+      </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
+      <c r="B22" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>57</v>
+      </c>
       <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="E22" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
+      <c r="B23" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
+      <c r="B24" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>62</v>
+      </c>
       <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="E24" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
+      <c r="B25" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>64</v>
+      </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
+      <c r="B26" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
+      <c r="E26" s="3" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
+      <c r="B27" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>69</v>
+      </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
+      <c r="B28" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
+      <c r="B29" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
     </row>

--- a/Mixed/1_zhouyf.xlsx
+++ b/Mixed/1_zhouyf.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\Mixed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6C56FF3-97C7-42F9-BC3C-6878BAD04C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A308BF7-1B94-4898-BADF-FBF9A56C03DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17520" yWindow="1005" windowWidth="20880" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17520" yWindow="330" windowWidth="20880" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="1-5" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="123">
   <si>
     <t>Fre</t>
   </si>
@@ -440,6 +440,275 @@
   </si>
   <si>
     <t>着迷；入迷；沉醉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ているところ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正在…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">原型+ところ-&gt;即将做… </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>た</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>型+ところ-&gt;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>間に</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>后接瞬间动作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>間 -&gt; 后接持续动作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~うちに + 意志</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>趁着…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~うちに + 不加意志：在…期间/过程中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~ようとしている</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>即将…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ようとする</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：试图…</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>〜ようにしている</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>努力做到…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~つつある</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正在变化过程中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~てはじめて</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只有…，才…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一类形容词-&gt;名词</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>「い」变为「さ」，「い」变为「み」</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ひどい</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>残酷的；严重的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>くせ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毛病；特征</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>～次第</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N+次第-&gt;取决于…；次第に-&gt;渐渐…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>～から～にかけて</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从…到…（大致范围）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>～にかけて-&gt;在…方面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~をはじめ-&gt;以…为首</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~からして</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>即使只抽取一个例子都是这样的，所以整体来看也当然如此</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>さすが</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>真不愧是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>だけ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)尽可能…(2)仅仅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)尽…(2)仅仅(3)只要…就…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>～限り(3)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>いつでも</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>随时</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>いつまでも</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-&gt;永远</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~限りでは</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>かぎ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~に限って</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>いじめる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>欺负</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)偏偏…(2)特别坚信</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>ほめる</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-&gt;赞扬，称赞</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1167,7 +1436,9 @@
       <c r="E21" s="3"/>
     </row>
     <row r="22" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A22" s="3"/>
+      <c r="A22" s="3">
+        <v>0</v>
+      </c>
       <c r="B22" s="3" t="s">
         <v>56</v>
       </c>
@@ -1180,7 +1451,9 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A23" s="3"/>
+      <c r="A23" s="3">
+        <v>0</v>
+      </c>
       <c r="B23" s="3" t="s">
         <v>58</v>
       </c>
@@ -1191,7 +1464,9 @@
       <c r="E23" s="3"/>
     </row>
     <row r="24" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A24" s="3"/>
+      <c r="A24" s="3">
+        <v>0</v>
+      </c>
       <c r="B24" s="3" t="s">
         <v>61</v>
       </c>
@@ -1204,7 +1479,9 @@
       </c>
     </row>
     <row r="25" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A25" s="3"/>
+      <c r="A25" s="3">
+        <v>0</v>
+      </c>
       <c r="B25" s="5" t="s">
         <v>63</v>
       </c>
@@ -1215,7 +1492,9 @@
       <c r="E25" s="3"/>
     </row>
     <row r="26" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="A26" s="3"/>
+      <c r="A26" s="3">
+        <v>0</v>
+      </c>
       <c r="B26" s="5" t="s">
         <v>65</v>
       </c>
@@ -1228,7 +1507,9 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A27" s="3"/>
+      <c r="A27" s="3">
+        <v>0</v>
+      </c>
       <c r="B27" s="3" t="s">
         <v>68</v>
       </c>
@@ -1239,7 +1520,9 @@
       <c r="E27" s="3"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A28" s="3"/>
+      <c r="A28" s="3">
+        <v>0</v>
+      </c>
       <c r="B28" s="3" t="s">
         <v>70</v>
       </c>
@@ -1250,7 +1533,9 @@
       <c r="E28" s="3"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A29" s="3"/>
+      <c r="A29" s="3">
+        <v>0</v>
+      </c>
       <c r="B29" s="3" t="s">
         <v>72</v>
       </c>
@@ -1260,145 +1545,285 @@
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
+    <row r="30" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A30" s="3">
+        <v>0</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>75</v>
+      </c>
       <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
+      <c r="E30" s="3" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
+      <c r="A31" s="3">
+        <v>0</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
+      <c r="E31" s="3" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
+      <c r="A32" s="3">
+        <v>0</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>81</v>
+      </c>
       <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
+      <c r="E32" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A33" s="3">
+        <v>0</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>84</v>
+      </c>
       <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
+      <c r="E33" s="4" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
+      <c r="A34" s="3">
+        <v>0</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>87</v>
+      </c>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
+      <c r="A35" s="3">
+        <v>0</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>89</v>
+      </c>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
+      <c r="A36" s="3">
+        <v>0</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>91</v>
+      </c>
       <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
+      <c r="E36" s="3" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A37" s="3"/>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
+      <c r="A37" s="3">
+        <v>0</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
+      <c r="A38" s="3">
+        <v>0</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>95</v>
+      </c>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
+      <c r="A39" s="3">
+        <v>0</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>97</v>
+      </c>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
+      <c r="A40" s="3">
+        <v>0</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
+      <c r="E40" s="3" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A41" s="3"/>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
+      <c r="A41" s="3">
+        <v>0</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>101</v>
+      </c>
       <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
+      <c r="E41" s="3" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
+      <c r="A42" s="3">
+        <v>0</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>105</v>
+      </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
+      <c r="A43" s="3">
+        <v>0</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>107</v>
+      </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A44" s="3"/>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
+      <c r="A44" s="3">
+        <v>0</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>109</v>
+      </c>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
+      <c r="A45" s="3">
+        <v>0</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
+      <c r="E45" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A46" s="3">
+        <v>0</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>113</v>
+      </c>
       <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
+      <c r="E46" s="4" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A47" s="3"/>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
+      <c r="A47" s="3">
+        <v>0</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>116</v>
+      </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A48" s="3"/>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
+      <c r="A48" s="3">
+        <v>0</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>121</v>
+      </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A49" s="3"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
+    <row r="49" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A49" s="3">
+        <v>0</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>120</v>
+      </c>
       <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
+      <c r="E49" s="5" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A50" s="3"/>

--- a/Mixed/1_zhouyf.xlsx
+++ b/Mixed/1_zhouyf.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\Mixed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A308BF7-1B94-4898-BADF-FBF9A56C03DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D1E8CA-83B2-4327-B4EF-504466628AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17520" yWindow="330" windowWidth="20880" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17520" yWindow="330" windowWidth="20880" windowHeight="19995" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-5" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="6-10" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="159">
   <si>
     <t>Fre</t>
   </si>
@@ -711,12 +711,168 @@
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>地方</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ちほう</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>偏远地区</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>相次いで</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>あいつ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>相继发生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>差別</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>さべつ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>歧视；区别对待</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~ばかりか</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不仅仅…还…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~はもとより</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>…自不必说</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>たばこ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>香烟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>及ぼす</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>およぼす</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>波及;影响</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ごちそうになる</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(我)受到款待；被请客</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ごちそうする</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(我)请客</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>同</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>「おごる」</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>～をめぐって</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>围绕着…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>とおり(2)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>和…一样;按照…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>でき上がります</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~をもとに</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以…为基础</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>断る(2)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提前告知;拒绝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~につけて</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一…就…；每当…</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>~につれて-&gt;伴随着</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -766,6 +922,13 @@
       <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -1862,9 +2025,173 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="23.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B2" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B3" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B4" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B5" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B6" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B7" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B8" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B9" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B11" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B12" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B13" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B14" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B15" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="B16" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Mixed/1_zhouyf.xlsx
+++ b/Mixed/1_zhouyf.xlsx
@@ -8,20 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\Mixed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E9E38B-A56F-4DA3-9334-F99110DC6750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01C07030-0A3D-4CF4-80AA-5D1340E3788E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17520" yWindow="330" windowWidth="20880" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14355" yWindow="585" windowWidth="20880" windowHeight="19995" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-10" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="11-20" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="208">
   <si>
     <t>Fre</t>
   </si>
@@ -164,347 +164,581 @@
     <t>刚…就…</t>
   </si>
   <si>
+    <t>～おかげで</t>
+  </si>
+  <si>
+    <t>(1)托…的福(2)都怪</t>
+  </si>
+  <si>
+    <t>~限りでは</t>
+  </si>
+  <si>
+    <t>根据…</t>
+  </si>
+  <si>
+    <t>いじめる</t>
+  </si>
+  <si>
+    <t>欺负</t>
+  </si>
+  <si>
+    <t>ほめる-&gt;赞扬，称赞</t>
+  </si>
+  <si>
+    <t>～限り(3)</t>
+  </si>
+  <si>
+    <t>(1)尽…(2)仅仅(3)只要…就…</t>
+  </si>
+  <si>
+    <t>かぎ</t>
+  </si>
+  <si>
+    <t>間に</t>
+  </si>
+  <si>
+    <t>后接瞬间动作</t>
+  </si>
+  <si>
+    <t>間 -&gt; 后接持续动作</t>
+  </si>
+  <si>
+    <t>ているところ</t>
+  </si>
+  <si>
+    <t>正在…</t>
+  </si>
+  <si>
+    <t>~ようとしている</t>
+  </si>
+  <si>
+    <t>即将…</t>
+  </si>
+  <si>
+    <t>ようとする：试图…</t>
+  </si>
+  <si>
+    <t>〜ようにしている</t>
+  </si>
+  <si>
+    <t>努力做到…</t>
+  </si>
+  <si>
+    <t>だけ</t>
+  </si>
+  <si>
+    <t>(1)尽可能…(2)仅仅</t>
+  </si>
+  <si>
+    <t>夢中</t>
+  </si>
+  <si>
+    <t>着迷；入迷；沉醉</t>
+  </si>
+  <si>
+    <t>~てはじめて</t>
+  </si>
+  <si>
+    <t>只有…，才…</t>
+  </si>
+  <si>
+    <t>~をはじめ-&gt;以…为首</t>
+  </si>
+  <si>
+    <t>~うちに + 意志</t>
+  </si>
+  <si>
+    <t>趁着…</t>
+  </si>
+  <si>
+    <t>ひどい</t>
+  </si>
+  <si>
+    <t>残酷的；严重的</t>
+  </si>
+  <si>
+    <t>くせ</t>
+  </si>
+  <si>
+    <t>毛病；特征</t>
+  </si>
+  <si>
+    <t>～次第</t>
+  </si>
+  <si>
+    <t>～ているうちに</t>
+  </si>
+  <si>
+    <t>在…过程中</t>
+  </si>
+  <si>
+    <t>~からして</t>
+  </si>
+  <si>
+    <t>即使只抽取一个例子都是这样的，所以整体来看也当然如此</t>
+  </si>
+  <si>
+    <t>さすが</t>
+  </si>
+  <si>
+    <t>真不愧是</t>
+  </si>
+  <si>
+    <t>～上(に)</t>
+  </si>
+  <si>
+    <t>不仅…而且…</t>
+  </si>
+  <si>
+    <t>～上で(は) -&gt; 在…方面</t>
+  </si>
+  <si>
+    <t>连用+次第</t>
+  </si>
+  <si>
+    <t>"刚…就…"一般不接人的意志，此处是例外</t>
+  </si>
+  <si>
+    <t>このごろ</t>
+  </si>
+  <si>
+    <t>最近；近来</t>
+  </si>
+  <si>
+    <t>～以上(は)</t>
+  </si>
+  <si>
+    <t>既然…就…</t>
+  </si>
+  <si>
+    <t>~つつある</t>
+  </si>
+  <si>
+    <t>正在变化过程中</t>
+  </si>
+  <si>
+    <t>～上で</t>
+  </si>
+  <si>
+    <t>在…之后</t>
+  </si>
+  <si>
+    <t>～ております</t>
+  </si>
+  <si>
+    <t>“～ている”自谦</t>
+  </si>
+  <si>
+    <t>しっかりと</t>
+  </si>
+  <si>
+    <t>让“稳稳地、扎实地”这种感觉变得更强调、更正式</t>
+  </si>
+  <si>
+    <t>~にあたって</t>
+  </si>
+  <si>
+    <t>当…时候</t>
+  </si>
+  <si>
+    <t>接续：辞书形</t>
+  </si>
+  <si>
+    <t>一类形容词-&gt;名词</t>
+  </si>
+  <si>
+    <t>「い」变为「さ」，「い」变为「み」</t>
+  </si>
+  <si>
+    <t>行う</t>
+  </si>
+  <si>
+    <t>做…事;举行，实行</t>
+  </si>
+  <si>
+    <t>おこなう</t>
+  </si>
+  <si>
+    <t>行なう</t>
+  </si>
+  <si>
+    <t>～から～にかけて</t>
+  </si>
+  <si>
+    <t>从…到…（大致范围）</t>
+  </si>
+  <si>
+    <t>～にかけて-&gt;在…方面</t>
+  </si>
+  <si>
+    <t>~ちゃんと</t>
+  </si>
+  <si>
+    <t>牢牢地；好好地</t>
+  </si>
+  <si>
+    <t>ちょっと-&gt;稍微；一会儿</t>
+  </si>
+  <si>
+    <t>相次いで</t>
+  </si>
+  <si>
+    <t>相继发生</t>
+  </si>
+  <si>
+    <t>あいつ</t>
+  </si>
+  <si>
+    <t>差別</t>
+  </si>
+  <si>
+    <t>歧视；区别对待</t>
+  </si>
+  <si>
+    <t>さべつ</t>
+  </si>
+  <si>
+    <t>~ばかりか</t>
+  </si>
+  <si>
+    <t>不仅仅…还…</t>
+  </si>
+  <si>
+    <t>~はもとより</t>
+  </si>
+  <si>
+    <t>…自不必说</t>
+  </si>
+  <si>
+    <t>ごちそうになる</t>
+  </si>
+  <si>
+    <t>(我)受到款待；被请客</t>
+  </si>
+  <si>
+    <t>～をめぐって</t>
+  </si>
+  <si>
+    <t>围绕着…</t>
+  </si>
+  <si>
+    <t>~をもとに</t>
+  </si>
+  <si>
+    <t>以…为基础</t>
+  </si>
+  <si>
+    <t>断る(2)</t>
+  </si>
+  <si>
+    <t>提前告知;拒绝</t>
+  </si>
+  <si>
+    <t>~につけて</t>
+  </si>
+  <si>
+    <t>一…就…；每当…</t>
+  </si>
+  <si>
+    <t>~につれて-&gt;伴随着</t>
+  </si>
+  <si>
+    <t>地方</t>
+  </si>
+  <si>
+    <t>偏远地区</t>
+  </si>
+  <si>
+    <t>ちほう</t>
+  </si>
+  <si>
+    <t>たばこ</t>
+  </si>
+  <si>
+    <t>香烟</t>
+  </si>
+  <si>
+    <t>及ぼす</t>
+  </si>
+  <si>
+    <t>波及;影响</t>
+  </si>
+  <si>
+    <t>およぼす</t>
+  </si>
+  <si>
+    <t>ごちそうする</t>
+  </si>
+  <si>
+    <t>(我)请客</t>
+  </si>
+  <si>
+    <t>同「おごる」</t>
+  </si>
+  <si>
+    <t>とおり(2)</t>
+  </si>
+  <si>
+    <t>和…一样;按照…</t>
+  </si>
+  <si>
+    <t>でき上がります</t>
+  </si>
+  <si>
+    <t>完成</t>
+  </si>
+  <si>
     <t>两处接同一个动词，第一处(原型/た型)，第二处ない形</t>
-  </si>
-  <si>
-    <t>～おかげで</t>
-  </si>
-  <si>
-    <t>(1)托…的福(2)都怪</t>
-  </si>
-  <si>
-    <t>~限りでは</t>
-  </si>
-  <si>
-    <t>根据…</t>
-  </si>
-  <si>
-    <t>いじめる</t>
-  </si>
-  <si>
-    <t>欺负</t>
-  </si>
-  <si>
-    <t>ほめる-&gt;赞扬，称赞</t>
-  </si>
-  <si>
-    <t>～限り(3)</t>
-  </si>
-  <si>
-    <t>(1)尽…(2)仅仅(3)只要…就…</t>
-  </si>
-  <si>
-    <t>かぎ</t>
-  </si>
-  <si>
-    <t>間に</t>
-  </si>
-  <si>
-    <t>后接瞬间动作</t>
-  </si>
-  <si>
-    <t>間 -&gt; 后接持续动作</t>
-  </si>
-  <si>
-    <t>ているところ</t>
-  </si>
-  <si>
-    <t>正在…</t>
-  </si>
-  <si>
-    <t>原型+ところ-&gt;即将做… た型+ところ-&gt;</t>
-  </si>
-  <si>
-    <t>~ようとしている</t>
-  </si>
-  <si>
-    <t>即将…</t>
-  </si>
-  <si>
-    <t>ようとする：试图…</t>
-  </si>
-  <si>
-    <t>〜ようにしている</t>
-  </si>
-  <si>
-    <t>努力做到…</t>
-  </si>
-  <si>
-    <t>だけ</t>
-  </si>
-  <si>
-    <t>(1)尽可能…(2)仅仅</t>
-  </si>
-  <si>
-    <t>夢中</t>
-  </si>
-  <si>
-    <t>着迷；入迷；沉醉</t>
-  </si>
-  <si>
-    <t>~てはじめて</t>
-  </si>
-  <si>
-    <t>只有…，才…</t>
-  </si>
-  <si>
-    <t>~をはじめ-&gt;以…为首</t>
-  </si>
-  <si>
-    <t>~うちに + 意志</t>
-  </si>
-  <si>
-    <t>趁着…</t>
-  </si>
-  <si>
-    <t>~うちに + 不加意志：在…期间/过程中</t>
-  </si>
-  <si>
-    <t>ひどい</t>
-  </si>
-  <si>
-    <t>残酷的；严重的</t>
-  </si>
-  <si>
-    <t>くせ</t>
-  </si>
-  <si>
-    <t>毛病；特征</t>
-  </si>
-  <si>
-    <t>～次第</t>
-  </si>
-  <si>
-    <t>N+次第-&gt;取决于…；次第に-&gt;渐渐…</t>
-  </si>
-  <si>
-    <t>～ているうちに</t>
-  </si>
-  <si>
-    <t>在…过程中</t>
-  </si>
-  <si>
-    <t>~からして</t>
-  </si>
-  <si>
-    <t>即使只抽取一个例子都是这样的，所以整体来看也当然如此</t>
-  </si>
-  <si>
-    <t>さすが</t>
-  </si>
-  <si>
-    <t>真不愧是</t>
-  </si>
-  <si>
-    <t>～上(に)</t>
-  </si>
-  <si>
-    <t>不仅…而且…</t>
-  </si>
-  <si>
-    <t>～上で(は) -&gt; 在…方面</t>
-  </si>
-  <si>
-    <t>连用+次第</t>
-  </si>
-  <si>
-    <t>"刚…就…"一般不接人的意志，此处是例外</t>
-  </si>
-  <si>
-    <t>このごろ</t>
-  </si>
-  <si>
-    <t>最近；近来</t>
-  </si>
-  <si>
-    <t>～以上(は)</t>
-  </si>
-  <si>
-    <t>既然…就…</t>
-  </si>
-  <si>
-    <t>~つつある</t>
-  </si>
-  <si>
-    <t>正在变化过程中</t>
-  </si>
-  <si>
-    <t>～上で</t>
-  </si>
-  <si>
-    <t>在…之后</t>
-  </si>
-  <si>
-    <t>～ております</t>
-  </si>
-  <si>
-    <t>“～ている”自谦</t>
-  </si>
-  <si>
-    <t>しっかりと</t>
-  </si>
-  <si>
-    <t>让“稳稳地、扎实地”这种感觉变得更强调、更正式</t>
-  </si>
-  <si>
-    <t>~にあたって</t>
-  </si>
-  <si>
-    <t>当…时候</t>
-  </si>
-  <si>
-    <t>接续：辞书形</t>
-  </si>
-  <si>
-    <t>一类形容词-&gt;名词</t>
-  </si>
-  <si>
-    <t>「い」变为「さ」，「い」变为「み」</t>
-  </si>
-  <si>
-    <t>行う</t>
-  </si>
-  <si>
-    <t>做…事;举行，实行</t>
-  </si>
-  <si>
-    <t>おこなう</t>
-  </si>
-  <si>
-    <t>行なう</t>
-  </si>
-  <si>
-    <t>～から～にかけて</t>
-  </si>
-  <si>
-    <t>从…到…（大致范围）</t>
-  </si>
-  <si>
-    <t>～にかけて-&gt;在…方面</t>
-  </si>
-  <si>
-    <t>~ちゃんと</t>
-  </si>
-  <si>
-    <t>牢牢地；好好地</t>
-  </si>
-  <si>
-    <t>ちょっと-&gt;稍微；一会儿</t>
-  </si>
-  <si>
-    <t>相次いで</t>
-  </si>
-  <si>
-    <t>相继发生</t>
-  </si>
-  <si>
-    <t>あいつ</t>
-  </si>
-  <si>
-    <t>差別</t>
-  </si>
-  <si>
-    <t>歧视；区别对待</t>
-  </si>
-  <si>
-    <t>さべつ</t>
-  </si>
-  <si>
-    <t>~ばかりか</t>
-  </si>
-  <si>
-    <t>不仅仅…还…</t>
-  </si>
-  <si>
-    <t>~はもとより</t>
-  </si>
-  <si>
-    <t>…自不必说</t>
-  </si>
-  <si>
-    <t>ごちそうになる</t>
-  </si>
-  <si>
-    <t>(我)受到款待；被请客</t>
-  </si>
-  <si>
-    <t>～をめぐって</t>
-  </si>
-  <si>
-    <t>围绕着…</t>
-  </si>
-  <si>
-    <t>~をもとに</t>
-  </si>
-  <si>
-    <t>以…为基础</t>
-  </si>
-  <si>
-    <t>断る(2)</t>
-  </si>
-  <si>
-    <t>提前告知;拒绝</t>
-  </si>
-  <si>
-    <t>~につけて</t>
-  </si>
-  <si>
-    <t>一…就…；每当…</t>
-  </si>
-  <si>
-    <t>~につれて-&gt;伴随着</t>
-  </si>
-  <si>
-    <t>地方</t>
-  </si>
-  <si>
-    <t>偏远地区</t>
-  </si>
-  <si>
-    <t>ちほう</t>
-  </si>
-  <si>
-    <t>たばこ</t>
-  </si>
-  <si>
-    <t>香烟</t>
-  </si>
-  <si>
-    <t>及ぼす</t>
-  </si>
-  <si>
-    <t>波及;影响</t>
-  </si>
-  <si>
-    <t>およぼす</t>
-  </si>
-  <si>
-    <t>ごちそうする</t>
-  </si>
-  <si>
-    <t>(我)请客</t>
-  </si>
-  <si>
-    <t>同「おごる」</t>
-  </si>
-  <si>
-    <t>とおり(2)</t>
-  </si>
-  <si>
-    <t>和…一样;按照…</t>
-  </si>
-  <si>
-    <t>でき上がります</t>
-  </si>
-  <si>
-    <t>完成</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>原型+ところ-&gt;即将做…    た型+ところ-&gt;刚刚</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>N+次第-&gt;取决于…；   次第に-&gt;渐渐…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~うちに + 不加意志：   在…期间/过程中</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~にかかわらず</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不论如何；不管怎样；</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>にもかかわらず</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>尽管；虽然</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~はさておき</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>暂且不论；姑且不论</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>せき</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>咳嗽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~ものか</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>绝对不…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>こつこつ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>孜孜不倦；坚持不懈</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>～わけがない</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>完全否定</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~わけではない</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>部分否定，并非；也不是</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>姿勢</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>态度；姿态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>しせい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>上場</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>じょうじょう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>上市</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>上昇</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>じょうしょう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>上升；增加</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>わがまま</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>任性；自私</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>とれる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>收获;取得；理解；</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>～を思いだす</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>想起(旧事)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>～を思い</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>つく</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>相出(idea)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~のこととなると</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>一提到…(后续接跟平时不同态度的句子)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>おば</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>姨妈；姑妈；</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>きょうだい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>兄弟姐妹</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>にあたる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>相当于</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>きつい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>辛苦的；严格；困难；</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~（よ）うものなら</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果…的话，后接坏事</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~ないことには</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果不…某事就无法实现</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>たとえ悪い結果にしろ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>"にしろ"同"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>でも</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -524,6 +758,13 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -561,10 +802,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1107,7 +1351,7 @@
         <v>46</v>
       </c>
       <c r="E18" t="s">
-        <v>47</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.15">
@@ -1115,10 +1359,10 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" t="s">
         <v>48</v>
-      </c>
-      <c r="C19" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.15">
@@ -1126,10 +1370,10 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" t="s">
         <v>50</v>
-      </c>
-      <c r="C20" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.15">
@@ -1137,13 +1381,13 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" t="s">
         <v>52</v>
       </c>
-      <c r="C21" t="s">
+      <c r="E21" t="s">
         <v>53</v>
-      </c>
-      <c r="E21" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.15">
@@ -1151,13 +1395,13 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" t="s">
         <v>55</v>
       </c>
-      <c r="C22" t="s">
+      <c r="E22" t="s">
         <v>56</v>
-      </c>
-      <c r="E22" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.15">
@@ -1165,13 +1409,13 @@
         <v>1</v>
       </c>
       <c r="B23" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" t="s">
         <v>58</v>
       </c>
-      <c r="C23" t="s">
+      <c r="E23" t="s">
         <v>59</v>
-      </c>
-      <c r="E23" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.15">
@@ -1179,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" t="s">
         <v>61</v>
       </c>
-      <c r="C24" t="s">
-        <v>62</v>
-      </c>
       <c r="E24" t="s">
-        <v>63</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.15">
@@ -1193,13 +1437,13 @@
         <v>1</v>
       </c>
       <c r="B25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" t="s">
         <v>64</v>
-      </c>
-      <c r="C25" t="s">
-        <v>65</v>
-      </c>
-      <c r="E25" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.15">
@@ -1207,10 +1451,10 @@
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.15">
@@ -1218,10 +1462,10 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.15">
@@ -1229,10 +1473,10 @@
         <v>1</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.15">
@@ -1240,13 +1484,13 @@
         <v>1</v>
       </c>
       <c r="B29" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" t="s">
+        <v>72</v>
+      </c>
+      <c r="E29" t="s">
         <v>73</v>
-      </c>
-      <c r="C29" t="s">
-        <v>74</v>
-      </c>
-      <c r="E29" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.15">
@@ -1254,13 +1498,13 @@
         <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E30" t="s">
-        <v>78</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.15">
@@ -1268,10 +1512,10 @@
         <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C31" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.15">
@@ -1279,10 +1523,10 @@
         <v>1</v>
       </c>
       <c r="B32" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C32" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.15">
@@ -1290,13 +1534,13 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C33" t="s">
         <v>20</v>
       </c>
       <c r="E33" t="s">
-        <v>84</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.15">
@@ -1304,10 +1548,10 @@
         <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C34" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.15">
@@ -1315,10 +1559,10 @@
         <v>1</v>
       </c>
       <c r="B35" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C35" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.15">
@@ -1326,10 +1570,10 @@
         <v>1</v>
       </c>
       <c r="B36" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C36" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.15">
@@ -1337,13 +1581,13 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C37" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E37" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.15">
@@ -1351,10 +1595,10 @@
         <v>0</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C38" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.15">
@@ -1362,10 +1606,10 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C39" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.15">
@@ -1373,10 +1617,10 @@
         <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C40" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.15">
@@ -1384,10 +1628,10 @@
         <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C41" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.15">
@@ -1395,13 +1639,13 @@
         <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C42" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E42" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.15">
@@ -1409,10 +1653,10 @@
         <v>0</v>
       </c>
       <c r="B43" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C43" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.15">
@@ -1420,10 +1664,10 @@
         <v>0</v>
       </c>
       <c r="B44" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C44" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.15">
@@ -1431,13 +1675,13 @@
         <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C45" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E45" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.15">
@@ -1445,10 +1689,10 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C46" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.15">
@@ -1456,16 +1700,16 @@
         <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C47" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D47" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E47" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.15">
@@ -1473,13 +1717,13 @@
         <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C48" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E48" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.15">
@@ -1487,13 +1731,13 @@
         <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C49" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E49" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.15">
@@ -1501,13 +1745,13 @@
         <v>1</v>
       </c>
       <c r="B50" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C50" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D50" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.15">
@@ -1515,13 +1759,13 @@
         <v>1</v>
       </c>
       <c r="B51" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C51" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D51" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.15">
@@ -1529,10 +1773,10 @@
         <v>1</v>
       </c>
       <c r="B52" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C52" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.15">
@@ -1540,10 +1784,10 @@
         <v>1</v>
       </c>
       <c r="B53" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C53" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.15">
@@ -1551,10 +1795,10 @@
         <v>1</v>
       </c>
       <c r="B54" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C54" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.15">
@@ -1562,10 +1806,10 @@
         <v>1</v>
       </c>
       <c r="B55" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C55" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.15">
@@ -1573,10 +1817,10 @@
         <v>1</v>
       </c>
       <c r="B56" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C56" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.15">
@@ -1584,10 +1828,10 @@
         <v>1</v>
       </c>
       <c r="B57" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C57" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.15">
@@ -1595,13 +1839,13 @@
         <v>1</v>
       </c>
       <c r="B58" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C58" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E58" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.15">
@@ -1609,13 +1853,13 @@
         <v>0</v>
       </c>
       <c r="B59" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C59" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D59" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.15">
@@ -1623,10 +1867,10 @@
         <v>0</v>
       </c>
       <c r="B60" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C60" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.15">
@@ -1634,13 +1878,13 @@
         <v>0</v>
       </c>
       <c r="B61" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C61" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D61" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.15">
@@ -1648,13 +1892,13 @@
         <v>0</v>
       </c>
       <c r="B62" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C62" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E62" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.15">
@@ -1662,10 +1906,10 @@
         <v>0</v>
       </c>
       <c r="B63" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C63" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.15">
@@ -1673,10 +1917,10 @@
         <v>0</v>
       </c>
       <c r="B64" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C64" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -1688,10 +1932,299 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="16.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="36.875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.25" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A3" s="2">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A4" s="2">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A5" s="2">
+        <v>0</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A6" s="2">
+        <v>0</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A7" s="2">
+        <v>0</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A8" s="2">
+        <v>0</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A9" s="2">
+        <v>0</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A10" s="2">
+        <v>0</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A11" s="2">
+        <v>0</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A12" s="2">
+        <v>0</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A13" s="2">
+        <v>0</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A14" s="2">
+        <v>0</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A15" s="2">
+        <v>0</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A16" s="2">
+        <v>0</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A17" s="2">
+        <v>0</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A18" s="2">
+        <v>0</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A19" s="2">
+        <v>0</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A20" s="2">
+        <v>0</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A21" s="2">
+        <v>0</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A22" s="2">
+        <v>0</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A23" s="2">
+        <v>0</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A24" s="2">
+        <v>0</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Mixed/1_zhouyf.xlsx
+++ b/Mixed/1_zhouyf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\Mixed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01C07030-0A3D-4CF4-80AA-5D1340E3788E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB931B88-1DB1-446B-BF06-59C2013C8421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14355" yWindow="585" windowWidth="20880" windowHeight="19995" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="223">
   <si>
     <t>Fre</t>
   </si>
@@ -733,12 +733,103 @@
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>~によって(2)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>手段；原因</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ダイヤ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>列车时刻表；钻石</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>N+不足</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ぶそく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>不足-&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ふそく</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>～もの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(结尾)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>原因</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ぼろぼろ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>破烂不堪；破破烂烂</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~につき</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>因为…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5つずつ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>每份五个</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -763,6 +854,20 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
       <charset val="128"/>
     </font>
@@ -802,12 +907,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1932,7 +2043,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -2134,7 +2245,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A17" s="2">
         <v>0</v>
       </c>
@@ -2145,7 +2256,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A18" s="2">
         <v>0</v>
       </c>
@@ -2156,7 +2267,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A19" s="2">
         <v>0</v>
       </c>
@@ -2167,7 +2278,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A20" s="2">
         <v>0</v>
       </c>
@@ -2178,7 +2289,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A21" s="2">
         <v>0</v>
       </c>
@@ -2189,7 +2300,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A22" s="2">
         <v>0</v>
       </c>
@@ -2200,7 +2311,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A23" s="2">
         <v>0</v>
       </c>
@@ -2211,7 +2322,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>0</v>
       </c>
@@ -2220,6 +2331,86 @@
       </c>
       <c r="C24" s="2" t="s">
         <v>207</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A25" s="2">
+        <v>0</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A26" s="2">
+        <v>0</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A27" s="2">
+        <v>0</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A28" s="2">
+        <v>0</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A29" s="2">
+        <v>0</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A30" s="2">
+        <v>0</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A31" s="2">
+        <v>0</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>

--- a/Mixed/1_zhouyf.xlsx
+++ b/Mixed/1_zhouyf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\Mixed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB931B88-1DB1-446B-BF06-59C2013C8421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5362F08-1116-4896-AD72-252DD84F8C7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14355" yWindow="585" windowWidth="20880" windowHeight="19995" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="225">
   <si>
     <t>Fre</t>
   </si>
@@ -822,6 +822,14 @@
   </si>
   <si>
     <t>每份五个</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>今まで</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>以往的</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2043,7 +2051,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -2413,6 +2421,17 @@
         <v>222</v>
       </c>
     </row>
+    <row r="32" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A32" s="2">
+        <v>0</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Mixed/1_zhouyf.xlsx
+++ b/Mixed/1_zhouyf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\Mixed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5362F08-1116-4896-AD72-252DD84F8C7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0EABC4C-B99E-415E-817E-7198E5785716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14355" yWindow="585" windowWidth="20880" windowHeight="19995" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14655" yWindow="15" windowWidth="20880" windowHeight="19995" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-10" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="236">
   <si>
     <t>Fre</t>
   </si>
@@ -830,6 +830,50 @@
   </si>
   <si>
     <t>以往的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>～ことだし</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>原因</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>してきまる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>做完某事就回来</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>でも</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>列举</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>いっそう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>更加</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>て・では</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)一类形容词-&gt;くて　(2)二类形容词/名词+で　(3)动词て型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>假设</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2051,7 +2095,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -2432,6 +2476,64 @@
         <v>224</v>
       </c>
     </row>
+    <row r="33" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A33" s="2">
+        <v>0</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A34" s="2">
+        <v>0</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A35" s="2">
+        <v>0</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A36" s="2">
+        <v>0</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A37" s="2">
+        <v>0</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Mixed/1_zhouyf.xlsx
+++ b/Mixed/1_zhouyf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\Mixed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0EABC4C-B99E-415E-817E-7198E5785716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F0F12E0-340C-4F5D-B05A-B8D3AF5C0E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14655" yWindow="15" windowWidth="20880" windowHeight="19995" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="274">
   <si>
     <t>Fre</t>
   </si>
@@ -874,6 +874,230 @@
   </si>
   <si>
     <t>假设</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>たい-&gt;想要</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>～が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>する</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>感到…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ホーム</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>站台；月台</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>名词+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>からなる</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>由…构成</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>パン</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>面包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>見舞い</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>みまい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>慰问；探望；问候</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ともすると</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>容易；往往</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ひどい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>残酷的；严重的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>普通形+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>とは</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>竟然</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>连用型+がたい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>何とも言いがたい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不知该怎么说</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>难以…(心理活动，而不是能力)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>に泊まる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>临时短住</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>连用型+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>かれる</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>难以…(委婉拒绝)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>连用+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ようがない</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)无法做某事….(2)完全否定</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>としか言いようがない</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>只能说是…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>文句</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>抱怨；牢骚</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>文句の付けようがない</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>无可挑剔；完美无缺</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>あり得ない</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>没可能</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>普通形+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>得る・得ない</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>能够/不能…</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2095,11 +2319,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="16.75" style="2" customWidth="1"/>
+    <col min="2" max="2" width="23.5" style="2" customWidth="1"/>
     <col min="3" max="3" width="36.875" style="2" customWidth="1"/>
     <col min="4" max="4" width="12.25" style="2" customWidth="1"/>
     <col min="5" max="5" width="14.25" style="2" customWidth="1"/>
@@ -2534,6 +2758,210 @@
         <v>234</v>
       </c>
     </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A38" s="2">
+        <v>0</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A39" s="2">
+        <v>0</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A40" s="2">
+        <v>0</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A41" s="2">
+        <v>0</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A42" s="2">
+        <v>0</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A43" s="2">
+        <v>0</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A44" s="2">
+        <v>0</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A45" s="2">
+        <v>0</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A46" s="2">
+        <v>0</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A47" s="2">
+        <v>0</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A48" s="2">
+        <v>0</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A49" s="2">
+        <v>0</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A50" s="2">
+        <v>0</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A51" s="2">
+        <v>0</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A52" s="2">
+        <v>0</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A53" s="2">
+        <v>0</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A54" s="2">
+        <v>0</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A55" s="2">
+        <v>0</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Mixed/1_zhouyf.xlsx
+++ b/Mixed/1_zhouyf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\Mixed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F0F12E0-340C-4F5D-B05A-B8D3AF5C0E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B807F1-D299-40BB-BAB0-BF362A42097C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14655" yWindow="15" windowWidth="20880" windowHeight="19995" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,21 @@
     <sheet name="1-10" sheetId="1" r:id="rId1"/>
     <sheet name="11-20" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="340">
   <si>
     <t>Fre</t>
   </si>
@@ -1100,12 +1109,373 @@
     <t>能够/不能…</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>立場</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>たちば</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>扱う</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>处理；对待</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>～わりに</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>轻微的转折，后接出乎意料的结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>～だけある</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>～だけのことわある</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>真不愧是...</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>真不愧是…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>常与"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>さすが</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"搭配</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>常与"さすが"搭配</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>さすが</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不愧是…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>面倒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>麻烦</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>面倒を見る</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>照顾；照料</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ありがたい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>值得感谢的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>原型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ところ</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ｖた＋ところ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ｖ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ている＋ところ</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>即将…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>正在…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚做完…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>たところ、…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在…之后</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>ｖた＋ところ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>で</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>即便…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>～きり</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>做了…后，一直处于某种状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>寝たきり</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>卧床不起</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>平均</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>へいきん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>寿命</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>じゅみょう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>接续是</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>た</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>型</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>～あげく</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在…之后(令人遗憾的结果)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>接续是た型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>及ぶ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>波及，长达</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>さんざん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>彻底地，拼命地</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>～末に</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在…之后(做了某个决断)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ついに</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>终于；最终</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>うっかり</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>无意中，差点就</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>危うい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>差点…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>〜ずじまいだ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>某事不了了之</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ラブレター</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>情书</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ず</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ずに</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>せず</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>せずに</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ない正式表达</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ないで正式表达</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>しない正式表达</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>しないで正式表达</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1147,6 +1517,13 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1183,7 +1560,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1195,6 +1572,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2319,13 +2699,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
     <col min="2" max="2" width="23.5" style="2" customWidth="1"/>
     <col min="3" max="3" width="36.875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="12.25" style="2" customWidth="1"/>
+    <col min="4" max="4" width="21.5" style="2" customWidth="1"/>
     <col min="5" max="5" width="14.25" style="2" customWidth="1"/>
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
@@ -2885,7 +3265,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A49" s="2">
         <v>0</v>
       </c>
@@ -2896,7 +3276,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A50" s="2">
         <v>0</v>
       </c>
@@ -2907,7 +3287,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A51" s="2">
         <v>0</v>
       </c>
@@ -2918,7 +3298,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A52" s="2">
         <v>0</v>
       </c>
@@ -2929,7 +3309,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A53" s="2">
         <v>0</v>
       </c>
@@ -2940,7 +3320,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A54" s="2">
         <v>0</v>
       </c>
@@ -2951,7 +3331,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
       <c r="A55" s="2">
         <v>0</v>
       </c>
@@ -2960,6 +3340,359 @@
       </c>
       <c r="C55" s="2" t="s">
         <v>273</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A56" s="2">
+        <v>0</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A57" s="2">
+        <v>0</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A58" s="2">
+        <v>0</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A59" s="2">
+        <v>0</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A60" s="2">
+        <v>0</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A61" s="2">
+        <v>0</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A62" s="2">
+        <v>0</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A63" s="2">
+        <v>0</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A64" s="2">
+        <v>0</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A65" s="2">
+        <v>0</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A66" s="2">
+        <v>0</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A67" s="2">
+        <v>0</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A68" s="2">
+        <v>0</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A69" s="2">
+        <v>0</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A70" s="2">
+        <v>0</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A71" s="2">
+        <v>0</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A72" s="2">
+        <v>0</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A73" s="2">
+        <v>0</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A74" s="2">
+        <v>0</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A75" s="2">
+        <v>0</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A76" s="2">
+        <v>0</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A77" s="2">
+        <v>0</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A78" s="2">
+        <v>0</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A79" s="2">
+        <v>0</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A80" s="2">
+        <v>0</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A81" s="2">
+        <v>0</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A82" s="2">
+        <v>0</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A83" s="2">
+        <v>0</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A84" s="2">
+        <v>0</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A85" s="2">
+        <v>0</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A86" s="2">
+        <v>0</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>339</v>
       </c>
     </row>
   </sheetData>

--- a/Mixed/1_zhouyf.xlsx
+++ b/Mixed/1_zhouyf.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\Mixed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B807F1-D299-40BB-BAB0-BF362A42097C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69B01B9D-787F-476F-A9F4-04BE75114B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14655" yWindow="15" windowWidth="20880" windowHeight="19995" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14655" yWindow="15" windowWidth="20880" windowHeight="19995" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1-10" sheetId="1" r:id="rId1"/>
     <sheet name="11-20" sheetId="3" r:id="rId2"/>
+    <sheet name="21-30" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="490">
   <si>
     <t>Fre</t>
   </si>
@@ -906,10 +907,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>感到…</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>ホーム</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1470,12 +1467,928 @@
     <t>しないで正式表达</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>～ぐらい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)最低程度…(2)大约，左右</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ぬれる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>淋湿；浸湿</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>〜など</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>诸如此类不重要的东西</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>～さえ～ば・たら・なら</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>只要…就…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>引っ張る</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ひっぱる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">拖拉拽 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(第一人称的五官)感到…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>がる-&gt;(第三人称心情)感到…</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>～きる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>把某动作做完</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>名词 + ぎみ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>稍微有点…的倾向</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ゆうべ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>昨晚</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>～かなにか</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>…之类的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>从…来看</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>からすると</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>〜からする</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ば</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>まじめに</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>认真；诚实；正经</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ぐらい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)程度(2)至少(3)大约</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>せめて</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>至少</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>たてもの</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>建筑物；房屋</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人びと</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>人们</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>むかえる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>迎接</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>それに</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>此外，再加上</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>そこで</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>于是…(紧接着做出了某个动作)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>そして</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>而且</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>”さえ”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>甚至</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>～とみえる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>推测…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>えさ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>饲料</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>～かれない</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>很可能…(坏结果)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>接续：连用型</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>～かれる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>难以…(委婉否定/拒绝)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>うわさ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>传闻；流言</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>～</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>まい</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ない</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"的书面语</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>肯定....</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>同"に違いない"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>おしゃれ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>时尚</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>主張</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>しゅちょう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>出張</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>しゅっちょう</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>証拠</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>しょうこ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>证据</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>に相違ない</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>〜に決まっている</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>しかる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>责备；训斥；斥责</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>にきまっている</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1)真理…(2)最好做…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>辞书</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ものだ</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ｖた＋もでだ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>怀念过去常做的事</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>というものだ</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>从常识开看，简直是…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>断る</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>事先告知</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>かい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>价值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>～にすぎない</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>只不过</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>…</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>とんでもない</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不用;哪里的话</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>〜にほかならない</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>正是…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ささえる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>支撑；支持</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>支える</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>に越したことはない</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最好是…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>辞书形</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>受け入れる</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>接受</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>〜べきだ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(社会常识或道德性)应该做某事</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>～はずだ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(可能形较高)推测</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>たいせつ</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>大切</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>重要</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>大切にする</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>珍惜；爱护</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>気軽に</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>轻松地；随意地</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>やはり</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>果然；毕竟</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>〜ことはない</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>没必要做某事</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>口を出す</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>くちをだす</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>插嘴；干预</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>〜ものか</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>完全否定，口语</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~てしかたがない</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>非常</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>非常…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~てしょうがない</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>主要是第三人称的话，要接"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>らしい</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>""</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ようだ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>主要是第三人称的话，要接"らしい""ようだ"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>かゆい</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>痒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~ないではいられない</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>情不自禁做某事</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~ずにはいられない</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>主要是第三人称的话，要接"そうだ"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~ないわけにはいかない</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(心理上)必须要做某事</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>辞书~わけにはいかない-&gt;不能做</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~ざるを得ない</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>接续:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ない</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>去掉</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>特例:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>する</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>せざる</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ポリシー</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>政策；方针</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>policy</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>N+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>には</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>对象</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的翻译</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>把…</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>税金</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ぜいきん</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>親戚</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>しんせき</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>どうにかして</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>想方设法、无论如何</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>なんて</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>竟然；这样的</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~ないものだろうか</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>难道不能…吗</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1524,6 +2437,37 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1560,7 +2504,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1575,6 +2519,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1879,7 +2834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -2688,6 +3643,163 @@
       </c>
       <c r="C64" t="s">
         <v>154</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A65">
+        <v>1</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="C65" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A66">
+        <v>1</v>
+      </c>
+      <c r="B66" t="s">
+        <v>354</v>
+      </c>
+      <c r="C66" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A67">
+        <v>1</v>
+      </c>
+      <c r="B67" t="s">
+        <v>356</v>
+      </c>
+      <c r="C67" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A68">
+        <v>1</v>
+      </c>
+      <c r="B68" t="s">
+        <v>358</v>
+      </c>
+      <c r="C68" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A69">
+        <v>1</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="C69" t="s">
+        <v>360</v>
+      </c>
+      <c r="E69" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A70">
+        <v>1</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="C70" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A71">
+        <v>1</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="C71" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A72">
+        <v>1</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="C72" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A73">
+        <v>1</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="C73" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A74">
+        <v>1</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="C74" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A75">
+        <v>1</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="C75" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A76">
+        <v>1</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="C76" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A77">
+        <v>1</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="C77" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A78">
+        <v>1</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="C78" t="s">
+        <v>380</v>
       </c>
     </row>
   </sheetData>
@@ -3143,10 +4255,10 @@
         <v>0</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>236</v>
@@ -3160,7 +4272,10 @@
         <v>237</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>238</v>
+        <v>350</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.15">
@@ -3168,10 +4283,10 @@
         <v>0</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
@@ -3179,10 +4294,10 @@
         <v>0</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.15">
@@ -3190,10 +4305,10 @@
         <v>0</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.15">
@@ -3201,13 +4316,13 @@
         <v>0</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.15">
@@ -3215,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.15">
@@ -3226,10 +4341,10 @@
         <v>0</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>250</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
@@ -3237,10 +4352,10 @@
         <v>0</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
@@ -3248,10 +4363,10 @@
         <v>0</v>
       </c>
       <c r="B47" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
@@ -3259,10 +4374,10 @@
         <v>0</v>
       </c>
       <c r="B48" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>258</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
@@ -3270,10 +4385,10 @@
         <v>0</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
@@ -3281,10 +4396,10 @@
         <v>0</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
@@ -3292,10 +4407,10 @@
         <v>0</v>
       </c>
       <c r="B51" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>264</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.15">
@@ -3303,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.15">
@@ -3314,10 +4429,10 @@
         <v>0</v>
       </c>
       <c r="B53" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>268</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
@@ -3325,10 +4440,10 @@
         <v>0</v>
       </c>
       <c r="B54" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
@@ -3336,10 +4451,10 @@
         <v>0</v>
       </c>
       <c r="B55" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
@@ -3347,10 +4462,10 @@
         <v>0</v>
       </c>
       <c r="B56" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>274</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.15">
@@ -3358,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="B57" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
@@ -3369,10 +4484,10 @@
         <v>0</v>
       </c>
       <c r="B58" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.15">
@@ -3380,13 +4495,13 @@
         <v>0</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
@@ -3394,13 +4509,13 @@
         <v>0</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>282</v>
-      </c>
       <c r="D60" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.15">
@@ -3408,10 +4523,10 @@
         <v>0</v>
       </c>
       <c r="B61" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>286</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.15">
@@ -3419,10 +4534,10 @@
         <v>0</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>288</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.15">
@@ -3430,10 +4545,10 @@
         <v>0</v>
       </c>
       <c r="B63" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.15">
@@ -3441,10 +4556,10 @@
         <v>0</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>292</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
@@ -3452,10 +4567,10 @@
         <v>0</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
@@ -3463,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
@@ -3474,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.15">
@@ -3485,10 +4600,10 @@
         <v>0</v>
       </c>
       <c r="B68" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
@@ -3496,10 +4611,10 @@
         <v>0</v>
       </c>
       <c r="B69" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>302</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
@@ -3507,13 +4622,13 @@
         <v>0</v>
       </c>
       <c r="B70" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="C70" s="2" t="s">
-        <v>305</v>
-      </c>
       <c r="D70" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.15">
@@ -3521,10 +4636,10 @@
         <v>0</v>
       </c>
       <c r="B71" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.15">
@@ -3532,10 +4647,10 @@
         <v>0</v>
       </c>
       <c r="B72" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.15">
@@ -3543,10 +4658,10 @@
         <v>0</v>
       </c>
       <c r="B73" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>310</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
@@ -3554,13 +4669,13 @@
         <v>0</v>
       </c>
       <c r="B74" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="D74" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
@@ -3568,10 +4683,10 @@
         <v>0</v>
       </c>
       <c r="B75" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.15">
@@ -3579,10 +4694,10 @@
         <v>0</v>
       </c>
       <c r="B76" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>318</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
@@ -3590,10 +4705,10 @@
         <v>0</v>
       </c>
       <c r="B77" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>320</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.15">
@@ -3601,10 +4716,10 @@
         <v>0</v>
       </c>
       <c r="B78" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>322</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.15">
@@ -3612,10 +4727,10 @@
         <v>0</v>
       </c>
       <c r="B79" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>324</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.15">
@@ -3623,10 +4738,10 @@
         <v>0</v>
       </c>
       <c r="B80" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.15">
@@ -3634,10 +4749,10 @@
         <v>0</v>
       </c>
       <c r="B81" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>328</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
@@ -3645,10 +4760,10 @@
         <v>0</v>
       </c>
       <c r="B82" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>330</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
@@ -3656,10 +4771,10 @@
         <v>0</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.15">
@@ -3667,10 +4782,10 @@
         <v>0</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.15">
@@ -3678,10 +4793,10 @@
         <v>0</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.15">
@@ -3689,10 +4804,10 @@
         <v>0</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -3700,4 +4815,681 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D13C35A-49F6-4E62-9150-87ECBEB16A38}">
+  <dimension ref="A1:E54"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="17.875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="25.125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A3" s="2">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A4" s="2">
+        <v>0</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A5" s="2">
+        <v>0</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A6" s="2">
+        <v>0</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A7" s="2">
+        <v>0</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A8" s="2">
+        <v>0</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A9" s="2">
+        <v>0</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A10" s="2">
+        <v>0</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A11" s="2">
+        <v>0</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A12" s="2">
+        <v>0</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>0</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A14" s="2">
+        <v>0</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A15" s="2">
+        <v>0</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A16" s="2">
+        <v>0</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A17" s="2">
+        <v>0</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>0</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A19" s="2">
+        <v>0</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>0</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A21" s="2">
+        <v>0</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A22" s="2">
+        <v>0</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A23" s="2">
+        <v>0</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A24" s="2">
+        <v>0</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A25" s="2">
+        <v>0</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A26" s="2">
+        <v>0</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A27" s="2">
+        <v>0</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A28" s="2">
+        <v>0</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A29" s="2">
+        <v>0</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A30" s="2">
+        <v>0</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A31" s="2">
+        <v>0</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A32" s="2">
+        <v>0</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A33" s="2">
+        <v>0</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A34" s="2">
+        <v>0</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A35" s="2">
+        <v>0</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A36" s="2">
+        <v>0</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A37" s="2">
+        <v>0</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A38" s="2">
+        <v>0</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A39" s="2">
+        <v>0</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A40" s="2">
+        <v>0</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A41" s="2">
+        <v>0</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A42" s="2">
+        <v>0</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A43" s="2">
+        <v>0</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A44" s="2">
+        <v>0</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A45" s="2">
+        <v>0</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A46" s="2">
+        <v>0</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A47" s="2">
+        <v>0</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A48" s="2">
+        <v>0</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A49" s="2">
+        <v>0</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A50" s="2">
+        <v>0</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A51" s="2">
+        <v>0</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A52" s="2">
+        <v>0</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A53" s="2">
+        <v>0</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A54" s="2">
+        <v>0</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Mixed/1_zhouyf.xlsx
+++ b/Mixed/1_zhouyf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\Mixed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69B01B9D-787F-476F-A9F4-04BE75114B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF698489-80D2-412D-8AC0-DB1ABC7EAB24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14655" yWindow="15" windowWidth="20880" windowHeight="19995" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4824,7 +4824,7 @@
   <cols>
     <col min="1" max="1" width="17.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="25.125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="39.25" style="2" customWidth="1"/>
     <col min="4" max="4" width="17.875" style="2" customWidth="1"/>
     <col min="5" max="5" width="15" style="2" customWidth="1"/>
     <col min="6" max="16384" width="9" style="2"/>

--- a/Mixed/1_zhouyf.xlsx
+++ b/Mixed/1_zhouyf.xlsx
@@ -467,7 +467,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -484,16 +484,16 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>名词 + ぎみ</t>
+          <t>せめて</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>稍微有点…的倾向</t>
+          <t>至少</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -501,37 +501,33 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>門出</t>
+          <t>まじめに</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>开始新生活</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>かどで</t>
-        </is>
-      </c>
+          <t>认真；诚实；正经</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>～かと思うと</t>
+          <t>〜ようにしている</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>刚…就…;本以为…却…</t>
+          <t>努力做到…</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -539,16 +535,16 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>いきなり</t>
+          <t>～かと思うと</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>突然地</t>
+          <t>刚…就…;本以为…却…</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -556,16 +552,16 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>～おかげで</t>
+          <t>~限りでは</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>(1)托…的福(2)都怪</t>
+          <t>根据…</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -573,16 +569,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>～あいだに</t>
+          <t>むかえる</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>在…期间</t>
+          <t>迎接</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -590,16 +586,16 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>そこで</t>
+          <t>ゆうべ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>于是…(紧接着做出了某个动作)</t>
+          <t>昨晚</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -607,33 +603,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>それに</t>
+          <t>差別</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>此外，再加上</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>歧视；区别对待</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>さべつ</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>むかえる</t>
+          <t>~ばかりか</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>迎接</t>
+          <t>不仅仅…还…</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -641,50 +641,58 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>人びと</t>
+          <t>~につけて</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>人们</t>
+          <t>一…就…；每当…</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>~につれて-&gt;伴随着</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>たてもの</t>
+          <t>~ようとしている</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>建筑物；房屋</t>
+          <t>即将…</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ようとする：试图…</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>せめて</t>
+          <t>たてもの</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>至少</t>
+          <t>建筑物；房屋</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -692,16 +700,16 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ぐらい</t>
+          <t>～きる</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>(1)程度(2)至少(3)大约</t>
+          <t>把某动作做完</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -709,16 +717,16 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>まじめに</t>
+          <t>名词 + ぎみ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>认真；诚实；正经</t>
+          <t>稍微有点…的倾向</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -726,16 +734,16 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ゆうべ</t>
+          <t>そこで</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>昨晚</t>
+          <t>于是…(紧接着做出了某个动作)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -747,12 +755,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>~に限って</t>
+          <t>～かなにか</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>(1)偏偏…(2)特别坚信</t>
+          <t>…之类的</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -764,16 +772,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>~限りでは</t>
+          <t>いつでも</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>根据…</t>
+          <t>随时</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>いつまでも-&gt;永远</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -781,20 +793,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>~てはじめて</t>
+          <t>~はもとより</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>只有…，才…</t>
+          <t>…自不必说</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>~をはじめ-&gt;以…为首</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -802,12 +810,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>~からして</t>
+          <t>くせ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>即使只抽取一个例子都是这样的，所以整体来看也当然如此</t>
+          <t>毛病；特征</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -819,18 +827,18 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ているところ</t>
+          <t>～限り(3)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>正在…</t>
+          <t>(1)尽…(2)仅仅(3)只要…就…</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>原型+ところ-&gt;即将做…    た型+ところ-&gt;刚刚</t>
+          <t>かぎ</t>
         </is>
       </c>
     </row>
@@ -840,12 +848,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>〜ようにしている</t>
+          <t>さすが</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>努力做到…</t>
+          <t>真不愧是</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -857,19 +865,15 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>差別</t>
+          <t>人びと</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>歧视；区别对待</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>さべつ</t>
-        </is>
-      </c>
+          <t>人们</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -878,12 +882,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>~ばかりか</t>
+          <t>それに</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>不仅仅…还…</t>
+          <t>此外，再加上</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -895,18 +899,18 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>~につけて</t>
+          <t>~てはじめて</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>一…就…；每当…</t>
+          <t>只有…，才…</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>~につれて-&gt;伴随着</t>
+          <t>~をはじめ-&gt;以…为首</t>
         </is>
       </c>
     </row>
@@ -916,20 +920,16 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>~ようとしている</t>
+          <t>~からして</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>即将…</t>
+          <t>即使只抽取一个例子都是这样的，所以整体来看也当然如此</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>ようとする：试图…</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -937,12 +937,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>~をもとに</t>
+          <t>～おかげで</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>以…为基础</t>
+          <t>(1)托…的福(2)都怪</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -954,12 +954,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>～きる</t>
+          <t>いきなり</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>把某动作做完</t>
+          <t>突然地</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -967,16 +967,16 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>夢中</t>
+          <t>ぐらい</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>着迷；入迷；沉醉</t>
+          <t>(1)程度(2)至少(3)大约</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -984,37 +984,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>いじめる</t>
+          <t>門出</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>欺负</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>ほめる-&gt;赞扬，称赞</t>
-        </is>
-      </c>
+          <t>开始新生活</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>かどで</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>お/ご+连用+になる</t>
+          <t>~に限って</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>尊他语</t>
+          <t>(1)偏偏…(2)特别坚信</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1022,16 +1022,16 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>だけ</t>
+          <t>~をもとに</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>(1)尽可能…(2)仅仅</t>
+          <t>以…为基础</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1039,16 +1039,16 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>~たとたん（に)</t>
+          <t>～あいだに</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>一…就…</t>
+          <t>在…期间</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1056,24 +1056,24 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>来日</t>
+          <t>ているところ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>访日</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>らいにち</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>正在…</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>原型+ところ-&gt;即将做…    た型+ところ-&gt;刚刚</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1081,18 +1081,18 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>間に</t>
+          <t>いじめる</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>后接瞬间动作</t>
+          <t>欺负</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>間 -&gt; 后接持续动作</t>
+          <t>ほめる-&gt;赞扬，称赞</t>
         </is>
       </c>
     </row>
@@ -1102,19 +1102,15 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>回る</t>
+          <t>お/ご+连用+になる</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>旋转；绕行；巡回</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>まわる</t>
-        </is>
-      </c>
+          <t>尊他语</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -1123,20 +1119,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>いつでも</t>
+          <t>~たとたん（に)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>随时</t>
+          <t>一…就…</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>いつまでも-&gt;永远</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1144,20 +1136,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>~にあたって</t>
+          <t>来日</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>当…时候</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>接续：辞书形</t>
-        </is>
-      </c>
+          <t>访日</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>らいにち</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1165,12 +1157,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>やさしい</t>
+          <t>～ているうちに</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>容易的</t>
+          <t>在…过程中</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1182,24 +1174,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>受け取る</t>
+          <t>だけ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>领取；理解；承担</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>うけとる</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>受付-&gt;うけつけ</t>
-        </is>
-      </c>
+          <t>(1)尽可能…(2)仅仅</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1207,20 +1191,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>中顿的三种方式</t>
+          <t>回る</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>て、连用、连用+まして</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>“连用”最正式</t>
-        </is>
-      </c>
+          <t>旋转；绕行；巡回</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>まわる</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1228,16 +1212,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>くせ</t>
+          <t>~にあたって</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>毛病；特征</t>
+          <t>当…时候</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>接续：辞书形</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1245,16 +1233,24 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>～ているうちに</t>
+          <t>受け取る</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>在…过程中</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+          <t>领取；理解；承担</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>うけとる</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>受付-&gt;うけつけ</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1262,18 +1258,18 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>あふれる</t>
+          <t>中顿的三种方式</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>充满；溢出</t>
+          <t>て、连用、连用+まして</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>溢れる</t>
+          <t>“连用”最正式</t>
         </is>
       </c>
     </row>
@@ -1283,16 +1279,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>さすが</t>
+          <t>~ちゃんと</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>真不愧是</t>
+          <t>牢牢地；好好地</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ちょっと-&gt;稍微；一会儿</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>お+连用+ください</t>
+          <t>夢中</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>「てください」尊他</t>
+          <t>着迷；入迷；沉醉</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1317,19 +1317,15 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>相次いで</t>
+          <t>ひどい</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>相继发生</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>あいつ</t>
-        </is>
-      </c>
+          <t>残酷的；严重的</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -1338,16 +1334,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>~はもとより</t>
+          <t>間に</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>…自不必说</t>
+          <t>后接瞬间动作</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>間 -&gt; 后接持续动作</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1355,16 +1355,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>～をめぐって</t>
+          <t>〜からすると</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>围绕着…</t>
+          <t>从…来看</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>〜からするば</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1372,16 +1376,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>断る(2)</t>
+          <t>あふれる</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>提前告知;拒绝</t>
+          <t>充满；溢出</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>溢れる</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1389,12 +1397,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ごちそうになる</t>
+          <t>～をめぐって</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>(我)受到款待；被请客</t>
+          <t>围绕着…</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -1406,12 +1414,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>～かなにか</t>
+          <t>ごちそうになる</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>…之类的</t>
+          <t>(我)受到款待；被请客</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -1423,18 +1431,18 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>〜からすると</t>
+          <t>~うちに + 意志</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>从…来看</t>
+          <t>趁着…</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>〜からするば</t>
+          <t>~うちに + 不加意志：   在…期间/过程中</t>
         </is>
       </c>
     </row>
@@ -1444,20 +1452,16 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>～次第</t>
+          <t>断る(2)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>一…就…</t>
+          <t>提前告知;拒绝</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>N+次第-&gt;取决于…；   次第に-&gt;渐渐…</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1465,16 +1469,20 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>そして</t>
+          <t>～次第</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>而且</t>
+          <t>一…就…</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>N+次第-&gt;取决于…；   次第に-&gt;渐渐…</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1482,12 +1490,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ひどい</t>
+          <t>そして</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>残酷的；严重的</t>
+          <t>而且</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -1499,18 +1507,18 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>～限り(3)</t>
+          <t>～か～ないかのうちに</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>(1)尽…(2)仅仅(3)只要…就…</t>
+          <t>刚…就…</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>かぎ</t>
+          <t>两处接同一个动词，第一处(原型/た型)，第二处ない形</t>
         </is>
       </c>
     </row>
@@ -1520,20 +1528,16 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>~うちに + 意志</t>
+          <t>お+连用+ください</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>趁着…</t>
+          <t>「てください」尊他</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>~うちに + 不加意志：   在…期间/过程中</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1541,36 +1545,36 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>～か～ないかのうちに</t>
+          <t>やさしい</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>刚…就…</t>
+          <t>容易的</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>两处接同一个动词，第一处(原型/た型)，第二处ない形</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>とおり(2)</t>
+          <t>相次いで</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>和…一样;按照…</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>相继发生</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>あいつ</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
@@ -1579,20 +1583,16 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>~ちゃんと</t>
+          <t>しっかりと</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>牢牢地；好好地</t>
+          <t>让“稳稳地、扎实地”这种感觉变得更强调、更正式</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>ちょっと-&gt;稍微；一会儿</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1600,20 +1600,16 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>～から～にかけて</t>
+          <t>とおり(2)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>从…到…（大致范围）</t>
+          <t>和…一样;按照…</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>～にかけて-&gt;在…方面</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1621,22 +1617,18 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>行う</t>
+          <t>～から～にかけて</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>做…事;举行，实行</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>おこなう</t>
-        </is>
-      </c>
+          <t>从…到…（大致范围）</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>行なう</t>
+          <t>～にかけて-&gt;在…方面</t>
         </is>
       </c>
     </row>
@@ -1646,20 +1638,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>地方</t>
+          <t>行う</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>偏远地区</t>
+          <t>做…事;举行，实行</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ちほう</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
+          <t>おこなう</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>行なう</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1667,15 +1663,19 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>たばこ</t>
+          <t>地方</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>香烟</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>偏远地区</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ちほう</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
@@ -1684,19 +1684,15 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>及ぼす</t>
+          <t>たばこ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>波及;影响</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>およぼす</t>
-        </is>
-      </c>
+          <t>香烟</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
@@ -1705,20 +1701,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ごちそうする</t>
+          <t>及ぼす</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>(我)请客</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>同「おごる」</t>
-        </is>
-      </c>
+          <t>波及;影响</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>およぼす</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1726,16 +1722,20 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>しっかりと</t>
+          <t>ごちそうする</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>让“稳稳地、扎实地”这种感觉变得更强调、更正式</t>
+          <t>(我)请客</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>同「おごる」</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>でき上がります</t>
+          <t>このごろ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>完成</t>
+          <t>最近；近来</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>このごろ</t>
+          <t>连用+次第</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>最近；近来</t>
+          <t>"刚…就…"一般不接人的意志，此处是例外</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -1849,16 +1849,20 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>连用+次第</t>
+          <t>～上(に)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>"刚…就…"一般不接人的意志，此处是例外</t>
+          <t>不仅…而且…</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>～上で(は) -&gt; 在…方面</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1866,20 +1870,16 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>～上(に)</t>
+          <t>でき上がります</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>不仅…而且…</t>
+          <t>完成</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>～上で(は) -&gt; 在…方面</t>
-        </is>
-      </c>
+      <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1949,7 +1949,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1966,16 +1966,16 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>危うい</t>
+          <t>にあたる</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>差点…</t>
+          <t>相当于</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -1983,16 +1983,16 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ついに</t>
+          <t>普通形+とは</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>终于；最终</t>
+          <t>竟然</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -2000,16 +2000,16 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>さんざん</t>
+          <t>ｖた＋ところで</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>彻底地，拼命地</t>
+          <t>即便…</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -2017,16 +2017,16 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>寿命</t>
+          <t>平均</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>じゅみょう</t>
+          <t>へいきん</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>平均</t>
+          <t>寿命</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>へいきん</t>
+          <t>じゅみょう</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -2051,16 +2051,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>寝たきり</t>
+          <t>こつこつ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>卧床不起</t>
+          <t>孜孜不倦；坚持不懈</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -2068,16 +2068,16 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ｖた＋ところで</t>
+          <t>ついに</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>即便…</t>
+          <t>终于；最终</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -2085,16 +2085,16 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>普通形+とは</t>
+          <t>せき</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>竟然</t>
+          <t>咳嗽</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -2102,16 +2102,16 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>立場</t>
+          <t>わがまま</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>たちば</t>
+          <t>任性；自私</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -2119,16 +2119,16 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>わがまま</t>
+          <t>とれる</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>任性；自私</t>
+          <t>收获;取得；理解；</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -2136,16 +2136,16 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>にあたる</t>
+          <t>せず</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>相当于</t>
+          <t>しない正式表达</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -2153,16 +2153,16 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>きょうだい</t>
+          <t>さすが</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>兄弟姐妹</t>
+          <t>不愧是…</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -2170,7 +2170,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2187,50 +2187,58 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>~のこととなると</t>
+          <t>～だけのことわある</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>一提到…(后续接跟平时不同态度的句子)</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>真不愧是...</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>常与"さすが"搭配</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>～を思いつく</t>
+          <t>～だけある</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>相出(idea)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>真不愧是…</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>常与"さすが"搭配</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>とれる</t>
+          <t>~ないことには</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>收获;取得；理解；</t>
+          <t>如果不…某事就无法实现</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -2238,37 +2246,33 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>見舞い</t>
+          <t>~はさておき</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>慰问；探望；问候</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>みまい</t>
-        </is>
-      </c>
+          <t>暂且不论；姑且不论</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>こつこつ</t>
+          <t>扱う</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>孜孜不倦；坚持不懈</t>
+          <t>处理；对待</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -2276,16 +2280,16 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>せき</t>
+          <t>〜ずじまいだ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>咳嗽</t>
+          <t>某事不了了之</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -2293,16 +2297,16 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>~はさておき</t>
+          <t>いっそう</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>暂且不论；姑且不论</t>
+          <t>更加</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -2310,16 +2314,16 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>~（よ）うものなら</t>
+          <t>してきまる</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>如果…的话，后接坏事</t>
+          <t>做完某事就回来</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -2327,16 +2331,16 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>~ないことには</t>
+          <t>～ことだし</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>如果不…某事就无法实现</t>
+          <t>原因</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -2348,12 +2352,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>いっそう</t>
+          <t>~のこととなると</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>更加</t>
+          <t>一提到…(后续接跟平时不同态度的句子)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -2365,12 +2369,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>してきまる</t>
+          <t>今まで</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>做完某事就回来</t>
+          <t>以往的</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -2382,12 +2386,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>～ことだし</t>
+          <t>连用型+かれる</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>原因</t>
+          <t>难以…(委婉拒绝)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2399,15 +2403,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ぼろぼろ</t>
+          <t>～あげく</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>破烂不堪；破破烂烂</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>在…之后(令人遗憾的结果)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>接续是た型</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -2416,15 +2424,19 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>うっかり</t>
+          <t>～きり</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>无意中，差点就</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>做了…后，一直处于某种状态</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>接续是た型</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
@@ -2433,15 +2445,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>せずに</t>
+          <t>見舞い</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>しないで正式表达</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>慰问；探望；问候</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>みまい</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -2450,12 +2466,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>〜ずじまいだ</t>
+          <t>～を思いつく</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>某事不了了之</t>
+          <t>相出(idea)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2467,12 +2483,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>たところ、…</t>
+          <t>きょうだい</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>在…之后</t>
+          <t>兄弟姐妹</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2484,12 +2500,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>扱う</t>
+          <t>寝たきり</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>处理；对待</t>
+          <t>卧床不起</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2501,19 +2517,15 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>～だけある</t>
+          <t>さんざん</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>真不愧是…</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>常与"さすが"搭配</t>
-        </is>
-      </c>
+          <t>彻底地，拼命地</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
@@ -2522,19 +2534,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>～だけのことわある</t>
+          <t>立場</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>真不愧是...</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>常与"さすが"搭配</t>
-        </is>
-      </c>
+          <t>たちば</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
@@ -2543,12 +2551,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>文句の付けようがない</t>
+          <t>たところ、…</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>无可挑剔；完美无缺</t>
+          <t>在…之后</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -2560,12 +2568,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>何とも言いがたい</t>
+          <t>~（よ）うものなら</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>不知该怎么说</t>
+          <t>如果…的话，后接坏事</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -2577,12 +2585,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>さすが</t>
+          <t>危うい</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>不愧是…</t>
+          <t>差点…</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -2594,12 +2602,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>せず</t>
+          <t>ぼろぼろ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>しない正式表达</t>
+          <t>破烂不堪；破破烂烂</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -2607,16 +2615,16 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5つずつ</t>
+          <t>何とも言いがたい</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>每份五个</t>
+          <t>不知该怎么说</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2624,16 +2632,16 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ダイヤ</t>
+          <t>文句の付けようがない</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>列车时刻表；钻石</t>
+          <t>无可挑剔；完美无缺</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2641,16 +2649,16 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>～わりに</t>
+          <t>せずに</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>轻微的转折，后接出乎意料的结果</t>
+          <t>しないで正式表达</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -2658,23 +2666,19 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>N+不足</t>
+          <t>うっかり</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ぶそく</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>不足-&gt;ふそく</t>
-        </is>
-      </c>
+          <t>无意中，差点就</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -2683,12 +2687,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>～もの(结尾)</t>
+          <t>ホーム</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>原因</t>
+          <t>站台；月台</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -2700,12 +2704,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>たとえ悪い結果にしろ</t>
+          <t>ありがたい</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>"にしろ"同"でも"</t>
+          <t>值得感谢的</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -2717,12 +2721,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>~によって(2)</t>
+          <t>パン</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>手段；原因</t>
+          <t>面包</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -2734,12 +2738,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>パン</t>
+          <t>~によって(2)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>面包</t>
+          <t>手段；原因</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -2751,12 +2755,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ありがたい</t>
+          <t>～わりに</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>值得感谢的</t>
+          <t>轻微的转折，后接出乎意料的结果</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -2768,12 +2772,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>名词+からなる</t>
+          <t>たとえ悪い結果にしろ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>由…构成</t>
+          <t>"にしろ"同"でも"</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -2785,15 +2789,19 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ホーム</t>
+          <t>N+不足</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>站台；月台</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>ぶそく</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>不足-&gt;ふそく</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
@@ -2823,19 +2831,15 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>连用型+がたい</t>
+          <t>ダイヤ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>难以…(心理活动，而不是能力)</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>たい-&gt;想要</t>
-        </is>
-      </c>
+          <t>列车时刻表；钻石</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -2844,19 +2848,15 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>て・では</t>
+          <t>名词+からなる</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>假设</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>(1)一类形容词-&gt;くて　(2)二类形容词/名词+で　(3)动词て型</t>
-        </is>
-      </c>
+          <t>由…构成</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>普通形+得る・得ない</t>
+          <t>でも</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>能够/不能…</t>
+          <t>列举</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -2882,12 +2882,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>でも</t>
+          <t>~わけではない</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>列举</t>
+          <t>部分否定，并非；也不是</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -2899,15 +2899,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>~につき</t>
+          <t>连用型+がたい</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>因为…</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>难以…(心理活动，而不是能力)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>たい-&gt;想要</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
@@ -2916,15 +2920,19 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>面倒</t>
+          <t>て・では</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>麻烦</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>假设</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>(1)一类形容词-&gt;くて　(2)二类形容词/名词+で　(3)动词て型</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
@@ -2933,12 +2941,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>面倒を見る</t>
+          <t>普通形+得る・得ない</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>照顾；照料</t>
+          <t>能够/不能…</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -2950,12 +2958,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>今まで</t>
+          <t>~につき</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>以往的</t>
+          <t>因为…</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -2967,12 +2975,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>~ものか</t>
+          <t>面倒</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>绝对不…</t>
+          <t>麻烦</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -2984,12 +2992,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>~わけではない</t>
+          <t>面倒を見る</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>部分否定，并非；也不是</t>
+          <t>照顾；照料</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -3001,12 +3009,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>～わけがない</t>
+          <t>~ものか</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>完全否定</t>
+          <t>绝对不…</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -3018,12 +3026,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>に泊まる</t>
+          <t>5つずつ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>临时短住</t>
+          <t>每份五个</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -3035,12 +3043,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ず</t>
+          <t>ｖている＋ところ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ない正式表达</t>
+          <t>正在…</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -3052,12 +3060,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>～末に</t>
+          <t>～わけがない</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>在…之后(做了某个决断)</t>
+          <t>完全否定</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -3069,12 +3077,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ずに</t>
+          <t>～もの(结尾)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ないで正式表达</t>
+          <t>原因</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -3086,12 +3094,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>及ぶ</t>
+          <t>～末に</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>波及，长达</t>
+          <t>在…之后(做了某个决断)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -3103,19 +3111,15 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>～あげく</t>
+          <t>にもかかわらず</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>在…之后(令人遗憾的结果)</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>接续是た型</t>
-        </is>
-      </c>
+          <t>尽管；虽然</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
@@ -3124,12 +3128,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ｖた＋ところ</t>
+          <t>原型+ところ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>刚做完…</t>
+          <t>即将…</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -3141,19 +3145,15 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>～きり</t>
+          <t>及ぶ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>做了…后，一直处于某种状态</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>接续是た型</t>
-        </is>
-      </c>
+          <t>波及，长达</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
@@ -3162,12 +3162,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ｖている＋ところ</t>
+          <t>ｖた＋ところ</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>正在…</t>
+          <t>刚做完…</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -3179,12 +3179,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>原型+ところ</t>
+          <t>ずに</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>即将…</t>
+          <t>ないで正式表达</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>にもかかわらず</t>
+          <t>ラブレター</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>尽管；虽然</t>
+          <t>情书</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ラブレター</t>
+          <t>ひどい</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>情书</t>
+          <t>残酷的；严重的</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>连用型+かれる</t>
+          <t>连用+ようがない</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>难以…(委婉拒绝)</t>
+          <t>(1)无法做某事….(2)完全否定</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -3264,12 +3264,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>连用+ようがない</t>
+          <t>としか言いようがない</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>(1)无法做某事….(2)完全否定</t>
+          <t>只能说是…</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -3281,12 +3281,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>としか言いようがない</t>
+          <t>文句</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>只能说是…</t>
+          <t>抱怨；牢骚</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -3298,12 +3298,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>文句</t>
+          <t>～を思いだす</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>抱怨；牢骚</t>
+          <t>想起(旧事)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -3315,12 +3315,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>～を思いだす</t>
+          <t>あり得ない</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>想起(旧事)</t>
+          <t>没可能</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -3332,15 +3332,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>あり得ない</t>
+          <t>上昇</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>没可能</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>じょうしょう</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>上升；增加</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
@@ -3349,17 +3353,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>上昇</t>
+          <t>上場</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>じょうしょう</t>
+          <t>じょうじょう</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>上升；增加</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
@@ -3370,15 +3374,19 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ひどい</t>
+          <t>姿勢</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>残酷的；严重的</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>态度；姿态</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>しせい</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
@@ -3387,19 +3395,15 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>上場</t>
+          <t>に泊まる</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>じょうじょう</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
+          <t>临时短住</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
@@ -3408,19 +3412,15 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>姿勢</t>
+          <t>ず</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>态度；姿态</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>しせい</t>
-        </is>
-      </c>
+          <t>ない正式表达</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
     </row>
     <row r="86">
@@ -3491,58 +3491,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ささえる</t>
+          <t>ぬれる</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>支撑；支持</t>
+          <t>淋湿；浸湿</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>支える</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>~ないわけにはいかない</t>
+          <t>～とみえる</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>(心理上)必须要做某事</t>
+          <t>推测…</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>辞书~わけにはいかない-&gt;不能做</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>えさ</t>
+          <t>うわさ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>饲料</t>
+          <t>传闻；流言</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -3550,16 +3542,16 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>～とみえる</t>
+          <t>どうにかして</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>推测…</t>
+          <t>想方设法、无论如何</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -3567,16 +3559,16 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>おしゃれ</t>
+          <t>しかる</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>时尚</t>
+          <t>责备；训斥；斥责</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -3584,96 +3576,100 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>証拠</t>
+          <t>〜ことはない</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>证据</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>しょうこ</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>没必要做某事</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>辞书形</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ぬれる</t>
+          <t>口を出す</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>淋湿；浸湿</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>插嘴；干预</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>くちをだす</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>に越したことはない</t>
+          <t>〜にきまっている</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>最好是…</t>
+          <t>肯定....</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>辞书形</t>
+          <t>〜に決まっている</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>〜にきまっている</t>
+          <t>証拠</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>肯定....</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>〜に決まっている</t>
-        </is>
-      </c>
+          <t>证据</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>しょうこ</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>しかる</t>
+          <t>かゆい</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>责备；训斥；斥责</t>
+          <t>痒</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -3681,16 +3677,16 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>どうにかして</t>
+          <t>やはり</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>想方设法、无论如何</t>
+          <t>果然；毕竟</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -3698,16 +3694,16 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>親戚</t>
+          <t>おしゃれ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>しんせき</t>
+          <t>时尚</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -3715,16 +3711,16 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>税金</t>
+          <t>ｖた＋もでだ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ぜいきん</t>
+          <t>怀念过去常做的事</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -3736,12 +3732,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>N+には</t>
+          <t>えさ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>对象</t>
+          <t>饲料</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -3753,16 +3749,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>うわさ</t>
+          <t>ささえる</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>传闻；流言</t>
+          <t>支撑；支持</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>支える</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ｖた＋もでだ</t>
+          <t>税金</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>怀念过去常做的事</t>
+          <t>ぜいきん</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -3787,18 +3787,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ポリシー</t>
+          <t>に越したことはない</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>政策；方针</t>
+          <t>最好是…</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>policy</t>
+          <t>辞书形</t>
         </is>
       </c>
     </row>
@@ -3808,12 +3808,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>やはり</t>
+          <t>親戚</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>果然；毕竟</t>
+          <t>しんせき</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>かゆい</t>
+          <t>N+には</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>痒</t>
+          <t>对象</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -3842,16 +3842,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>〜べきだ</t>
+          <t>ポリシー</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>(社会常识或道德性)应该做某事</t>
+          <t>政策；方针</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3859,12 +3863,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>かい</t>
+          <t>〜べきだ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>价值</t>
+          <t>(社会常识或道德性)应该做某事</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -3876,12 +3880,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>～はずだ</t>
+          <t>かい</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>(可能形较高)推测</t>
+          <t>价值</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -3893,19 +3897,15 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>口を出す</t>
+          <t>～はずだ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>插嘴；干预</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>くちをだす</t>
-        </is>
-      </c>
+          <t>(可能形较高)推测</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -3914,18 +3914,18 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>〜ことはない</t>
+          <t>~ないではいられない</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>没必要做某事</t>
+          <t>情不自禁做某事</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>辞书形</t>
+          <t>主要是第三人称的话，要接"そうだ"</t>
         </is>
       </c>
     </row>
@@ -3935,20 +3935,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>~ないではいられない</t>
+          <t>気軽に</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>情不自禁做某事</t>
+          <t>轻松地；随意地</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>主要是第三人称的话，要接"そうだ"</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3956,16 +3952,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>気軽に</t>
+          <t>~ないわけにはいかない</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>轻松地；随意地</t>
+          <t>(心理上)必须要做某事</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>辞书~わけにはいかない-&gt;不能做</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>主張</t>
+          <t>～にすぎない</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>しゅちょう</t>
+          <t>只不过…</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -4011,18 +4011,18 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>〜に相違ない</t>
+          <t>～かれる</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>肯定....</t>
+          <t>难以…(委婉否定/拒绝)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>同"に違いない"</t>
+          <t>接续：连用型</t>
         </is>
       </c>
     </row>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>〜というものだ</t>
+          <t>～ぐらい</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>从常识开看，简直是…</t>
+          <t>(1)最低程度…(2)大约，左右</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -4049,12 +4049,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>出張</t>
+          <t>～まい</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>しゅっちょう</t>
+          <t>"ない"的书面语</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -4066,12 +4066,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>とんでもない</t>
+          <t>断る</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>不用;哪里的话</t>
+          <t>事先告知</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -4083,16 +4083,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>～にすぎない</t>
+          <t>〜に相違ない</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>只不过…</t>
+          <t>肯定....</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>同"に違いない"</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4100,12 +4104,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>断る</t>
+          <t>とんでもない</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>事先告知</t>
+          <t>不用;哪里的话</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -4117,12 +4121,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>辞书〜ものだ</t>
+          <t>出張</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>(1)真理…(2)最好做…</t>
+          <t>しゅっちょう</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -4134,12 +4138,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>～まい</t>
+          <t>〜というものだ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>"ない"的书面语</t>
+          <t>从常识开看，简直是…</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -4151,15 +4155,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>～ぐらい</t>
+          <t>引っ張る</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>(1)最低程度…(2)大约，左右</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t xml:space="preserve">拖拉拽 </t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ひっぱる</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -4168,20 +4176,16 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>～かれる</t>
+          <t>主張</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>难以…(委婉否定/拒绝)</t>
+          <t>しゅちょう</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>接续：连用型</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4210,20 +4214,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>引っ張る</t>
+          <t>~てしかたがない</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">拖拉拽 </t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>ひっぱる</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
+          <t>非常…</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>主要是第三人称的话，要接"らしい""ようだ"</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4231,20 +4235,16 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>～さえ～ば・たら・なら</t>
+          <t>辞书〜ものだ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>只要…就…</t>
+          <t>(1)真理…(2)最好做…</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>”さえ”甚至</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4269,16 +4269,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>〜にほかならない</t>
+          <t>～さえ～ば・たら・なら</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>正是…</t>
+          <t>只要…就…</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>”さえ”甚至</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4286,12 +4290,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>受け入れる</t>
+          <t>〜ものか</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>接受</t>
+          <t>完全否定，口语</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -4303,16 +4307,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>なんて</t>
+          <t>~てしょうがない</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>竟然；这样的</t>
+          <t>非常</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>主要是第三人称的话，要接"らしい""ようだ"</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4320,16 +4328,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>を的翻译</t>
+          <t>~ずにはいられない</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>把…</t>
+          <t>情不自禁做某事</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>主要是第三人称的话，要接"そうだ"</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4337,20 +4349,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>~ざるを得ない</t>
+          <t>大切にする</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>接续:ない去掉</t>
+          <t>珍惜；爱护</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>特例:する-&gt;せざる</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4358,20 +4366,16 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>~ずにはいられない</t>
+          <t>を的翻译</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>情不自禁做某事</t>
+          <t>把…</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>主要是第三人称的话，要接"そうだ"</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4379,20 +4383,16 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>~てしょうがない</t>
+          <t>なんて</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>非常</t>
+          <t>竟然；这样的</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>主要是第三人称的话，要接"らしい""ようだ"</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4400,20 +4400,16 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>~てしかたがない</t>
+          <t>受け入れる</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>非常…</t>
+          <t>接受</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>主要是第三人称的话，要接"らしい""ようだ"</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4421,12 +4417,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>〜ものか</t>
+          <t>〜にほかならない</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>完全否定，口语</t>
+          <t>正是…</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -4438,16 +4434,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>大切にする</t>
+          <t>~ざるを得ない</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>珍惜；爱护</t>
+          <t>接续:ない去掉</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>特例:する-&gt;せざる</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">

--- a/Mixed/1_zhouyf.xlsx
+++ b/Mixed/1_zhouyf.xlsx
@@ -467,16 +467,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>めまい</t>
+          <t>名词 + ぎみ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>头晕</t>
+          <t>稍微有点…的倾向</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -484,7 +484,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -501,16 +501,16 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>まじめに</t>
+          <t>たてもの</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>认真；诚实；正经</t>
+          <t>建筑物；房屋</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -518,16 +518,16 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>〜ようにしている</t>
+          <t>むかえる</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>努力做到…</t>
+          <t>迎接</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -535,16 +535,16 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>～かと思うと</t>
+          <t>～きる</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>刚…就…;本以为…却…</t>
+          <t>把某动作做完</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -552,33 +552,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>~限りでは</t>
+          <t>~につけて</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>根据…</t>
+          <t>一…就…；每当…</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>~につれて-&gt;伴随着</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>むかえる</t>
+          <t>まじめに</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>迎接</t>
+          <t>认真；诚实；正经</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -586,7 +590,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -603,37 +607,33 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>差別</t>
+          <t>〜ようにしている</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>歧视；区别对待</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>さべつ</t>
-        </is>
-      </c>
+          <t>努力做到…</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>~ばかりか</t>
+          <t>めまい</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>不仅仅…还…</t>
+          <t>头晕</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -641,58 +641,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>~につけて</t>
+          <t>いきなり</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>一…就…；每当…</t>
+          <t>突然地</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>~につれて-&gt;伴随着</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>~ようとしている</t>
+          <t>~はもとより</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>即将…</t>
+          <t>…自不必说</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>ようとする：试图…</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>たてもの</t>
+          <t>～かと思うと</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>建筑物；房屋</t>
+          <t>刚…就…;本以为…却…</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -700,16 +692,16 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>～きる</t>
+          <t>~ばかりか</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>把某动作做完</t>
+          <t>不仅仅…还…</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -717,50 +709,58 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>名词 + ぎみ</t>
+          <t>差別</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>稍微有点…的倾向</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>歧视；区别对待</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>さべつ</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>そこで</t>
+          <t>~ようとしている</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>于是…(紧接着做出了某个动作)</t>
+          <t>即将…</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ようとする：试图…</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>～かなにか</t>
+          <t>~限りでは</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>…之类的</t>
+          <t>根据…</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -768,54 +768,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>いつでも</t>
+          <t>さすが</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>随时</t>
+          <t>真不愧是</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>いつまでも-&gt;永远</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>~はもとより</t>
+          <t>〜からすると</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>…自不必说</t>
+          <t>从…来看</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>〜からするば</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>くせ</t>
+          <t>それに</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>毛病；特征</t>
+          <t>此外，再加上</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -823,54 +823,54 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>～限り(3)</t>
+          <t>そこで</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>(1)尽…(2)仅仅(3)只要…就…</t>
+          <t>于是…(紧接着做出了某个动作)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>かぎ</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>さすが</t>
+          <t>いつでも</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>真不愧是</t>
+          <t>随时</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>いつまでも-&gt;永远</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>人びと</t>
+          <t>～かなにか</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>人们</t>
+          <t>…之类的</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -878,54 +878,58 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>それに</t>
+          <t>～限り(3)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>此外，再加上</t>
+          <t>(1)尽…(2)仅仅(3)只要…就…</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>かぎ</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>~てはじめて</t>
+          <t>ているところ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>只有…，才…</t>
+          <t>正在…</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>~をはじめ-&gt;以…为首</t>
+          <t>原型+ところ-&gt;即将做…    た型+ところ-&gt;刚刚</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>~からして</t>
+          <t>~をもとに</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>即使只抽取一个例子都是这样的，所以整体来看也当然如此</t>
+          <t>以…为基础</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -937,15 +941,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>～おかげで</t>
+          <t>門出</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>(1)托…的福(2)都怪</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>开始新生活</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>かどで</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -954,12 +962,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>いきなり</t>
+          <t>~たとたん（に)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>突然地</t>
+          <t>一…就…</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -971,12 +979,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ぐらい</t>
+          <t>~に限って</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>(1)程度(2)至少(3)大约</t>
+          <t>(1)偏偏…(2)特别坚信</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -988,19 +996,15 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>門出</t>
+          <t>やさしい</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>开始新生活</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>かどで</t>
-        </is>
-      </c>
+          <t>容易的</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -1009,12 +1013,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>~に限って</t>
+          <t>くせ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>(1)偏偏…(2)特别坚信</t>
+          <t>毛病；特征</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1026,12 +1030,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>~をもとに</t>
+          <t>～おかげで</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>以…为基础</t>
+          <t>(1)托…的福(2)都怪</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1043,12 +1047,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>～あいだに</t>
+          <t>~からして</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>在…期间</t>
+          <t>即使只抽取一个例子都是这样的，所以整体来看也当然如此</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -1060,54 +1064,50 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ているところ</t>
+          <t>~てはじめて</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>正在…</t>
+          <t>只有…，才…</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>原型+ところ-&gt;即将做…    た型+ところ-&gt;刚刚</t>
+          <t>~をはじめ-&gt;以…为首</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>いじめる</t>
+          <t>人びと</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>欺负</t>
+          <t>人们</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>ほめる-&gt;赞扬，称赞</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>お/ご+连用+になる</t>
+          <t>～あいだに</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>尊他语</t>
+          <t>在…期间</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1115,40 +1115,40 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>~たとたん（に)</t>
+          <t>~にあたって</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>一…就…</t>
+          <t>当…时候</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>接续：辞书形</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>来日</t>
+          <t>ぐらい</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>访日</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>らいにち</t>
-        </is>
-      </c>
+          <t>(1)程度(2)至少(3)大约</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>～ているうちに</t>
+          <t>お/ご+连用+になる</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>在…过程中</t>
+          <t>尊他语</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1174,16 +1174,24 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>だけ</t>
+          <t>受け取る</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>(1)尽可能…(2)仅仅</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+          <t>领取；理解；承担</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>うけとる</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>受付-&gt;うけつけ</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1191,20 +1199,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>回る</t>
+          <t>~ちゃんと</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>旋转；绕行；巡回</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>まわる</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>牢牢地；好好地</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>ちょっと-&gt;稍微；一会儿</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1212,20 +1220,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>~にあたって</t>
+          <t>回る</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>当…时候</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>接续：辞书形</t>
-        </is>
-      </c>
+          <t>旋转；绕行；巡回</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>まわる</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1233,24 +1241,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>受け取る</t>
+          <t>だけ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>领取；理解；承担</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>うけとる</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>受付-&gt;うけつけ</t>
-        </is>
-      </c>
+          <t>(1)尽可能…(2)仅仅</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1258,20 +1258,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>中顿的三种方式</t>
+          <t>来日</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>て、连用、连用+まして</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>“连用”最正式</t>
-        </is>
-      </c>
+          <t>访日</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>らいにち</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1279,20 +1279,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>~ちゃんと</t>
+          <t>～ているうちに</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>牢牢地；好好地</t>
+          <t>在…过程中</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>ちょっと-&gt;稍微；一会儿</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1300,16 +1296,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>夢中</t>
+          <t>中顿的三种方式</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>着迷；入迷；沉醉</t>
+          <t>て、连用、连用+まして</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>“连用”最正式</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ひどい</t>
+          <t>～をめぐって</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>残酷的；严重的</t>
+          <t>围绕着…</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -1334,18 +1334,18 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>間に</t>
+          <t>～か～ないかのうちに</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>后接瞬间动作</t>
+          <t>刚…就…</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>間 -&gt; 后接持续动作</t>
+          <t>两处接同一个动词，第一处(原型/た型)，第二处ない形</t>
         </is>
       </c>
     </row>
@@ -1355,18 +1355,18 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>〜からすると</t>
+          <t>ごちそうする</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>从…来看</t>
+          <t>(我)请客</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>〜からするば</t>
+          <t>同「おごる」</t>
         </is>
       </c>
     </row>
@@ -1376,20 +1376,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>あふれる</t>
+          <t>相次いで</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>充满；溢出</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>溢れる</t>
-        </is>
-      </c>
+          <t>相继发生</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>あいつ</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>～をめぐって</t>
+          <t>夢中</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>围绕着…</t>
+          <t>着迷；入迷；沉醉</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -1414,16 +1414,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ごちそうになる</t>
+          <t>あふれる</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>(我)受到款待；被请客</t>
+          <t>充满；溢出</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>溢れる</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1452,12 +1456,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>断る(2)</t>
+          <t>ごちそうになる</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>提前告知;拒绝</t>
+          <t>(我)受到款待；被请客</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -1490,12 +1494,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>そして</t>
+          <t>断る(2)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>而且</t>
+          <t>提前告知;拒绝</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -1507,18 +1511,18 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>～か～ないかのうちに</t>
+          <t>間に</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>刚…就…</t>
+          <t>后接瞬间动作</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>两处接同一个动词，第一处(原型/た型)，第二处ない形</t>
+          <t>間 -&gt; 后接持续动作</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1549,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>やさしい</t>
+          <t>そして</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>容易的</t>
+          <t>而且</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -1562,37 +1566,37 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>相次いで</t>
+          <t>ひどい</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>相继发生</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>あいつ</t>
-        </is>
-      </c>
+          <t>残酷的；严重的</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>しっかりと</t>
+          <t>いじめる</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>让“稳稳地、扎实地”这种感觉变得更强调、更正式</t>
+          <t>欺负</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>ほめる-&gt;赞扬，称赞</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1600,12 +1604,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>とおり(2)</t>
+          <t>このごろ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>和…一样;按照…</t>
+          <t>最近；近来</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -1617,20 +1621,16 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>～から～にかけて</t>
+          <t>连用+次第</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>从…到…（大致范围）</t>
+          <t>"刚…就…"一般不接人的意志，此处是例外</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>～にかけて-&gt;在…方面</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1638,24 +1638,16 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>行う</t>
+          <t>とおり(2)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>做…事;举行，实行</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>おこなう</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>行なう</t>
-        </is>
-      </c>
+          <t>和…一样;按照…</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1663,20 +1655,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>地方</t>
+          <t>行う</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>偏远地区</t>
+          <t>做…事;举行，实行</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ちほう</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
+          <t>おこなう</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>行なう</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1684,15 +1680,19 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>たばこ</t>
+          <t>地方</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>香烟</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>偏远地区</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ちほう</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
@@ -1701,19 +1701,15 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>及ぼす</t>
+          <t>たばこ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>波及;影响</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>およぼす</t>
-        </is>
-      </c>
+          <t>香烟</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
@@ -1722,20 +1718,20 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ごちそうする</t>
+          <t>及ぼす</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>(我)请客</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>同「おごる」</t>
-        </is>
-      </c>
+          <t>波及;影响</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>およぼす</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1743,16 +1739,20 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>このごろ</t>
+          <t>～上(に)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>最近；近来</t>
+          <t>不仅…而且…</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>～上で(は) -&gt; 在…方面</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1760,16 +1760,20 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>一类形容词-&gt;名词</t>
+          <t>～から～にかけて</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>「い」变为「さ」，「い」变为「み」</t>
+          <t>从…到…（大致范围）</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>～にかけて-&gt;在…方面</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1832,12 +1836,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>连用+次第</t>
+          <t>でき上がります</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>"刚…就…"一般不接人的意志，此处是例外</t>
+          <t>完成</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -1849,20 +1853,16 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>～上(に)</t>
+          <t>一类形容词-&gt;名词</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>不仅…而且…</t>
+          <t>「い」变为「さ」，「い」变为「み」</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>～上で(は) -&gt; 在…方面</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>でき上がります</t>
+          <t>しっかりと</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>完成</t>
+          <t>让“稳稳地、扎实地”这种感觉变得更强调、更正式</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -1949,16 +1949,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ともすると</t>
+          <t>ついに</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>容易；往往</t>
+          <t>终于；最终</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -1966,16 +1966,16 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>にあたる</t>
+          <t>~はさておき</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>相当于</t>
+          <t>暂且不论；姑且不论</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -1983,16 +1983,16 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>普通形+とは</t>
+          <t>にあたる</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>竟然</t>
+          <t>相当于</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -2000,16 +2000,16 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ｖた＋ところで</t>
+          <t>ともすると</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>即便…</t>
+          <t>容易；往往</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -2017,16 +2017,16 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>平均</t>
+          <t>してきまる</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>へいきん</t>
+          <t>做完某事就回来</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -2034,16 +2034,16 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>寿命</t>
+          <t>せず</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>じゅみょう</t>
+          <t>しない正式表达</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -2051,16 +2051,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>こつこつ</t>
+          <t>わがまま</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>孜孜不倦；坚持不懈</t>
+          <t>任性；自私</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -2068,16 +2068,16 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ついに</t>
+          <t>とれる</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>终于；最终</t>
+          <t>收获;取得；理解；</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -2085,50 +2085,58 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>せき</t>
+          <t>～だけある</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>咳嗽</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>真不愧是…</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>常与"さすが"搭配</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>わがまま</t>
+          <t>～だけのことわある</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>任性；自私</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>真不愧是...</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>常与"さすが"搭配</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>とれる</t>
+          <t>寿命</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>收获;取得；理解；</t>
+          <t>じゅみょう</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -2136,16 +2144,16 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>せず</t>
+          <t>立場</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>しない正式表达</t>
+          <t>たちば</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -2153,16 +2161,16 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>さすが</t>
+          <t>平均</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>不愧是…</t>
+          <t>へいきん</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -2170,16 +2178,16 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>おば</t>
+          <t>普通形+とは</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>姨妈；姑妈；</t>
+          <t>竟然</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -2187,58 +2195,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>～だけのことわある</t>
+          <t>せき</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>真不愧是...</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>常与"さすが"搭配</t>
-        </is>
-      </c>
+          <t>咳嗽</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>～だけある</t>
+          <t>ｖた＋ところで</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>真不愧是…</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>常与"さすが"搭配</t>
-        </is>
-      </c>
+          <t>即便…</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>~ないことには</t>
+          <t>こつこつ</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>如果不…某事就无法实现</t>
+          <t>孜孜不倦；坚持不懈</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -2246,16 +2246,16 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>~はさておき</t>
+          <t>〜ずじまいだ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>暂且不论；姑且不论</t>
+          <t>某事不了了之</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -2263,16 +2263,16 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>扱う</t>
+          <t>おば</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>处理；对待</t>
+          <t>姨妈；姑妈；</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -2280,16 +2280,16 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>〜ずじまいだ</t>
+          <t>~ないことには</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>某事不了了之</t>
+          <t>如果不…某事就无法实现</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -2297,7 +2297,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>してきまる</t>
+          <t>～ことだし</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>做完某事就回来</t>
+          <t>原因</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -2335,29 +2335,33 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>～ことだし</t>
+          <t>見舞い</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>原因</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>慰问；探望；问候</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>みまい</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>~のこととなると</t>
+          <t>ぼろぼろ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>一提到…(后续接跟平时不同态度的句子)</t>
+          <t>破烂不堪；破破烂烂</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -2365,16 +2369,16 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>今まで</t>
+          <t>さんざん</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>以往的</t>
+          <t>彻底地，拼命地</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -2382,16 +2386,16 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>连用型+かれる</t>
+          <t>きょうだい</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>难以…(委婉拒绝)</t>
+          <t>兄弟姐妹</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2399,79 +2403,67 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>～あげく</t>
+          <t>~のこととなると</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>在…之后(令人遗憾的结果)</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>接续是た型</t>
-        </is>
-      </c>
+          <t>一提到…(后续接跟平时不同态度的句子)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>～きり</t>
+          <t>さすが</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>做了…后，一直处于某种状态</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>接续是た型</t>
-        </is>
-      </c>
+          <t>不愧是…</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>見舞い</t>
+          <t>扱う</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>慰问；探望；问候</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>みまい</t>
-        </is>
-      </c>
+          <t>处理；对待</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>～を思いつく</t>
+          <t>何とも言いがたい</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>相出(idea)</t>
+          <t>不知该怎么说</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2483,12 +2475,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>きょうだい</t>
+          <t>危うい</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>兄弟姐妹</t>
+          <t>差点…</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2500,12 +2492,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>寝たきり</t>
+          <t>今まで</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>卧床不起</t>
+          <t>以往的</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2517,12 +2509,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>さんざん</t>
+          <t>连用型+かれる</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>彻底地，拼命地</t>
+          <t>难以…(委婉拒绝)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -2534,15 +2526,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>立場</t>
+          <t>～あげく</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>たちば</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>在…之后(令人遗憾的结果)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>接续是た型</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
@@ -2551,12 +2547,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>たところ、…</t>
+          <t>～を思いつく</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>在…之后</t>
+          <t>相出(idea)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -2585,12 +2581,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>危うい</t>
+          <t>きつい</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>差点…</t>
+          <t>辛苦的；严格；困难；</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -2602,12 +2598,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ぼろぼろ</t>
+          <t>文句の付けようがない</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>破烂不堪；破破烂烂</t>
+          <t>无可挑剔；完美无缺</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -2619,12 +2615,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>何とも言いがたい</t>
+          <t>せずに</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>不知该怎么说</t>
+          <t>しないで正式表达</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2636,12 +2632,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>文句の付けようがない</t>
+          <t>寝たきり</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>无可挑剔；完美无缺</t>
+          <t>卧床不起</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2653,15 +2649,19 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>せずに</t>
+          <t>～きり</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>しないで正式表达</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>做了…后，一直处于某种状态</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>接续是た型</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
@@ -2683,16 +2683,16 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ホーム</t>
+          <t>たところ、…</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>站台；月台</t>
+          <t>在…之后</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -2704,12 +2704,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ありがたい</t>
+          <t>面倒を見る</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>值得感谢的</t>
+          <t>照顾；照料</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -2721,12 +2721,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>パン</t>
+          <t>名词+からなる</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>面包</t>
+          <t>由…构成</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -2738,15 +2738,19 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>~によって(2)</t>
+          <t>て・では</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>手段；原因</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>假设</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>(1)一类形容词-&gt;くて　(2)二类形容词/名词+で　(3)动词て型</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
@@ -2755,12 +2759,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>～わりに</t>
+          <t>ありがたい</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>轻微的转折，后接出乎意料的结果</t>
+          <t>值得感谢的</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -2772,12 +2776,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>たとえ悪い結果にしろ</t>
+          <t>パン</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>"にしろ"同"でも"</t>
+          <t>面包</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -2789,19 +2793,15 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>N+不足</t>
+          <t>~によって(2)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ぶそく</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>不足-&gt;ふそく</t>
-        </is>
-      </c>
+          <t>手段；原因</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
@@ -2810,19 +2810,15 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>～がする</t>
+          <t>～わりに</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>(第一人称的五官)感到…</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>〜がる-&gt;(第三人称心情)感到…</t>
-        </is>
-      </c>
+          <t>轻微的转折，后接出乎意料的结果</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
@@ -2831,12 +2827,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ダイヤ</t>
+          <t>たとえ悪い結果にしろ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>列车时刻表；钻石</t>
+          <t>"にしろ"同"でも"</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -2848,15 +2844,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>名词+からなる</t>
+          <t>N+不足</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>由…构成</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>ぶそく</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>不足-&gt;ふそく</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>でも</t>
+          <t>5つずつ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>列举</t>
+          <t>每份五个</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -2882,12 +2882,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>~わけではない</t>
+          <t>ダイヤ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>部分否定，并非；也不是</t>
+          <t>列车时刻表；钻石</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -2899,19 +2899,15 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>连用型+がたい</t>
+          <t>~ものか</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>难以…(心理活动，而不是能力)</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>たい-&gt;想要</t>
-        </is>
-      </c>
+          <t>绝对不…</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
@@ -2920,19 +2916,15 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>て・では</t>
+          <t>あり得ない</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>假设</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>(1)一类形容词-&gt;くて　(2)二类形容词/名词+で　(3)动词て型</t>
-        </is>
-      </c>
+          <t>没可能</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
@@ -2941,12 +2933,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>普通形+得る・得ない</t>
+          <t>~わけではない</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>能够/不能…</t>
+          <t>部分否定，并非；也不是</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -2958,15 +2950,19 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>~につき</t>
+          <t>连用型+がたい</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>因为…</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>难以…(心理活动，而不是能力)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>たい-&gt;想要</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
@@ -2975,12 +2971,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>面倒</t>
+          <t>ホーム</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>麻烦</t>
+          <t>站台；月台</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -2992,12 +2988,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>面倒を見る</t>
+          <t>普通形+得る・得ない</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>照顾；照料</t>
+          <t>能够/不能…</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -3009,12 +3005,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>~ものか</t>
+          <t>~につき</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>绝对不…</t>
+          <t>因为…</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -3026,12 +3022,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5つずつ</t>
+          <t>ｖている＋ところ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>每份五个</t>
+          <t>正在…</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -3043,15 +3039,19 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ｖている＋ところ</t>
+          <t>～がする</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>正在…</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>(第一人称的五官)感到…</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>〜がる-&gt;(第三人称心情)感到…</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
@@ -3060,15 +3060,19 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>～わけがない</t>
+          <t>姿勢</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>完全否定</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>态度；姿态</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>しせい</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
@@ -3077,12 +3081,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>～もの(结尾)</t>
+          <t>面倒</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>原因</t>
+          <t>麻烦</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -3094,12 +3098,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>～末に</t>
+          <t>ラブレター</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>在…之后(做了某个决断)</t>
+          <t>情书</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -3111,12 +3115,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>にもかかわらず</t>
+          <t>ず</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>尽管；虽然</t>
+          <t>ない正式表达</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -3128,12 +3132,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>原型+ところ</t>
+          <t>ひどい</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>即将…</t>
+          <t>残酷的；严重的</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -3145,12 +3149,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>及ぶ</t>
+          <t>～末に</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>波及，长达</t>
+          <t>在…之后(做了某个决断)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -3162,12 +3166,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ｖた＋ところ</t>
+          <t>にもかかわらず</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>刚做完…</t>
+          <t>尽管；虽然</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -3179,12 +3183,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ずに</t>
+          <t>原型+ところ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ないで正式表达</t>
+          <t>即将…</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -3196,12 +3200,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ラブレター</t>
+          <t>及ぶ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>情书</t>
+          <t>波及，长达</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -3213,12 +3217,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>きつい</t>
+          <t>ｖた＋ところ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>辛苦的；严格；困难；</t>
+          <t>刚做完…</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -3230,12 +3234,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ひどい</t>
+          <t>ずに</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>残酷的；严重的</t>
+          <t>ないで正式表达</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -3247,12 +3251,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>连用+ようがない</t>
+          <t>文句</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>(1)无法做某事….(2)完全否定</t>
+          <t>抱怨；牢骚</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -3264,12 +3268,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>としか言いようがない</t>
+          <t>～を思いだす</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>只能说是…</t>
+          <t>想起(旧事)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -3281,12 +3285,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>文句</t>
+          <t>～もの(结尾)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>抱怨；牢骚</t>
+          <t>原因</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -3298,12 +3302,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>～を思いだす</t>
+          <t>としか言いようがない</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>想起(旧事)</t>
+          <t>只能说是…</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -3315,12 +3319,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>あり得ない</t>
+          <t>でも</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>没可能</t>
+          <t>列举</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -3332,19 +3336,15 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>上昇</t>
+          <t>连用+ようがない</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>じょうしょう</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>上升；增加</t>
-        </is>
-      </c>
+          <t>(1)无法做某事….(2)完全否定</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
@@ -3353,19 +3353,15 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>上場</t>
+          <t>～わけがない</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>じょうじょう</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
+          <t>完全否定</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
     </row>
     <row r="83">
@@ -3374,17 +3370,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>姿勢</t>
+          <t>上昇</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>态度；姿态</t>
+          <t>じょうしょう</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>しせい</t>
+          <t>上升；增加</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
@@ -3395,15 +3391,19 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>に泊まる</t>
+          <t>上場</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>临时短住</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>じょうじょう</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
@@ -3412,12 +3412,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ず</t>
+          <t>に泊まる</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ない正式表达</t>
+          <t>临时短住</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -3491,16 +3491,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ぬれる</t>
+          <t>ｖた＋もでだ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>淋湿；浸湿</t>
+          <t>怀念过去常做的事</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -3508,16 +3508,16 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>～とみえる</t>
+          <t>うわさ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>推测…</t>
+          <t>传闻；流言</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -3525,16 +3525,16 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>うわさ</t>
+          <t>ぬれる</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>传闻；流言</t>
+          <t>淋湿；浸湿</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -3542,33 +3542,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>どうにかして</t>
+          <t>〜にきまっている</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>想方设法、无论如何</t>
+          <t>肯定....</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>〜に決まっている</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>しかる</t>
+          <t>おしゃれ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>责备；训斥；斥责</t>
+          <t>时尚</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -3576,100 +3580,92 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>〜ことはない</t>
+          <t>やはり</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>没必要做某事</t>
+          <t>果然；毕竟</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>辞书形</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>口を出す</t>
+          <t>証拠</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>插嘴；干预</t>
+          <t>证据</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>くちをだす</t>
+          <t>しょうこ</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>〜にきまっている</t>
+          <t>かゆい</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>肯定....</t>
+          <t>痒</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>〜に決まっている</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>証拠</t>
+          <t>口を出す</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>证据</t>
+          <t>插嘴；干预</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>しょうこ</t>
+          <t>くちをだす</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>かゆい</t>
+          <t>しかる</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>痒</t>
+          <t>责备；训斥；斥责</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -3681,16 +3677,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>やはり</t>
+          <t>ポリシー</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>果然；毕竟</t>
+          <t>政策；方针</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -3698,16 +3698,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>おしゃれ</t>
+          <t>ささえる</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>时尚</t>
+          <t>支撑；支持</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>支える</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -3715,29 +3719,33 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ｖた＋もでだ</t>
+          <t>に越したことはない</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>怀念过去常做的事</t>
+          <t>最好是…</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>辞书形</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>えさ</t>
+          <t>N+には</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>饲料</t>
+          <t>对象</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -3745,62 +3753,58 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ささえる</t>
+          <t>～とみえる</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>支撑；支持</t>
+          <t>推测…</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>支える</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>税金</t>
+          <t>〜ことはない</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ぜいきん</t>
+          <t>没必要做某事</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>辞书形</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>に越したことはない</t>
+          <t>どうにかして</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>最好是…</t>
+          <t>想方设法、无论如何</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>辞书形</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3825,12 +3829,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>N+には</t>
+          <t>気軽に</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>对象</t>
+          <t>轻松地；随意地</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -3842,20 +3846,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ポリシー</t>
+          <t>えさ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>政策；方针</t>
+          <t>饲料</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>policy</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>〜べきだ</t>
+          <t>税金</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>(社会常识或道德性)应该做某事</t>
+          <t>ぜいきん</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -3880,16 +3880,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>かい</t>
+          <t>~ないわけにはいかない</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>价值</t>
+          <t>(心理上)必须要做某事</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>辞书~わけにはいかない-&gt;不能做</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3897,12 +3901,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>～はずだ</t>
+          <t>〜べきだ</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>(可能形较高)推测</t>
+          <t>(社会常识或道德性)应该做某事</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -3914,20 +3918,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>~ないではいられない</t>
+          <t>かい</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>情不自禁做某事</t>
+          <t>价值</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>主要是第三人称的话，要接"そうだ"</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>気軽に</t>
+          <t>～はずだ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>轻松地；随意地</t>
+          <t>(可能形较高)推测</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -3952,20 +3952,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>~ないわけにはいかない</t>
+          <t>大切</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>(心理上)必须要做某事</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>辞书~わけにはいかない-&gt;不能做</t>
-        </is>
-      </c>
+          <t>重要</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>たいせつ</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3973,20 +3973,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>大切</t>
+          <t>~ないではいられない</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>重要</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>たいせつ</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>情不自禁做某事</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>主要是第三人称的话，要接"そうだ"</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3994,16 +3994,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>～にすぎない</t>
+          <t>〜に相違ない</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>只不过…</t>
+          <t>肯定....</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>同"に違いない"</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4011,20 +4015,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>～かれる</t>
+          <t>主張</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>难以…(委婉否定/拒绝)</t>
+          <t>しゅちょう</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>接续：连用型</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>～ぐらい</t>
+          <t>〜というものだ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>(1)最低程度…(2)大约，左右</t>
+          <t>从常识开看，简直是…</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -4049,12 +4049,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>～まい</t>
+          <t>出張</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>"ない"的书面语</t>
+          <t>しゅっちょう</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -4066,12 +4066,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>断る</t>
+          <t>とんでもない</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>事先告知</t>
+          <t>不用;哪里的话</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -4083,20 +4083,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>〜に相違ない</t>
+          <t>～まい</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>肯定....</t>
+          <t>"ない"的书面语</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>同"に違いない"</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4104,12 +4100,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>とんでもない</t>
+          <t>断る</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>不用;哪里的话</t>
+          <t>事先告知</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -4121,12 +4117,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>出張</t>
+          <t>～ぐらい</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>しゅっちょう</t>
+          <t>(1)最低程度…(2)大约，左右</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -4138,16 +4134,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>〜というものだ</t>
+          <t>～かれる</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>从常识开看，简直是…</t>
+          <t>难以…(委婉否定/拒绝)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>接续：连用型</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4155,19 +4155,15 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>引っ張る</t>
+          <t>～にすぎない</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">拖拉拽 </t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>ひっぱる</t>
-        </is>
-      </c>
+          <t>只不过…</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -4176,16 +4172,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>主張</t>
+          <t>~てしかたがない</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>しゅちょう</t>
+          <t>非常…</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>主要是第三人称的话，要接"らしい""ようだ"</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4214,20 +4214,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>~てしかたがない</t>
+          <t>を的翻译</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>非常…</t>
+          <t>把…</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>主要是第三人称的话，要接"らしい""ようだ"</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4235,15 +4231,19 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>辞书〜ものだ</t>
+          <t>引っ張る</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>(1)真理…(2)最好做…</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t xml:space="preserve">拖拉拽 </t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ひっぱる</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
@@ -4269,18 +4269,18 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>～さえ～ば・たら・なら</t>
+          <t>~ざるを得ない</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>只要…就…</t>
+          <t>接续:ない去掉</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>”さえ”甚至</t>
+          <t>特例:する-&gt;せざる</t>
         </is>
       </c>
     </row>
@@ -4290,12 +4290,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>〜ものか</t>
+          <t>〜にほかならない</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>完全否定，口语</t>
+          <t>正是…</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -4307,20 +4307,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>~てしょうがない</t>
+          <t>辞书〜ものだ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>非常</t>
+          <t>(1)真理…(2)最好做…</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>主要是第三人称的话，要接"らしい""ようだ"</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4328,20 +4324,16 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>~ずにはいられない</t>
+          <t>なんて</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>情不自禁做某事</t>
+          <t>竟然；这样的</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>主要是第三人称的话，要接"そうだ"</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4349,12 +4341,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>大切にする</t>
+          <t>受け入れる</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>珍惜；爱护</t>
+          <t>接受</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -4366,16 +4358,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>を的翻译</t>
+          <t>~ずにはいられない</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>把…</t>
+          <t>情不自禁做某事</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>主要是第三人称的话，要接"そうだ"</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4383,16 +4379,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>なんて</t>
+          <t>~てしょうがない</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>竟然；这样的</t>
+          <t>非常</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>主要是第三人称的话，要接"らしい""ようだ"</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>受け入れる</t>
+          <t>〜ものか</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>接受</t>
+          <t>完全否定，口语</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -4417,16 +4417,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>〜にほかならない</t>
+          <t>～さえ～ば・たら・なら</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>正是…</t>
+          <t>只要…就…</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>”さえ”甚至</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4434,20 +4438,16 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>~ざるを得ない</t>
+          <t>大切にする</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>接续:ない去掉</t>
+          <t>珍惜；爱护</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>特例:する-&gt;せざる</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">

--- a/Mixed/1_zhouyf.xlsx
+++ b/Mixed/1_zhouyf.xlsx
@@ -467,16 +467,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>名词 + ぎみ</t>
+          <t>せめて</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>稍微有点…的倾向</t>
+          <t>至少</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -484,16 +484,16 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>せめて</t>
+          <t>名词 + ぎみ</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>至少</t>
+          <t>稍微有点…的倾向</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -501,7 +501,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -518,16 +518,16 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>むかえる</t>
+          <t>めまい</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>迎接</t>
+          <t>头晕</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -535,16 +535,16 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>～きる</t>
+          <t>〜ようにしている</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>把某动作做完</t>
+          <t>努力做到…</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -552,37 +552,33 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>~につけて</t>
+          <t>ゆうべ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>一…就…；每当…</t>
+          <t>昨晚</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>~につれて-&gt;伴随着</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>まじめに</t>
+          <t>それに</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>认真；诚实；正经</t>
+          <t>此外，再加上</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -590,16 +586,16 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ゆうべ</t>
+          <t>まじめに</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>昨晚</t>
+          <t>认真；诚实；正经</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -607,20 +603,24 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>〜ようにしている</t>
+          <t>~につけて</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>努力做到…</t>
+          <t>一…就…；每当…</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>~につれて-&gt;伴随着</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -628,12 +628,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>めまい</t>
+          <t>～きる</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>头晕</t>
+          <t>把某动作做完</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -641,33 +641,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>いきなり</t>
+          <t>差別</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>突然地</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>歧视；区别对待</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>さべつ</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>~はもとより</t>
+          <t>むかえる</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>…自不必说</t>
+          <t>迎接</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -675,33 +679,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>～かと思うと</t>
+          <t>~ようとしている</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>刚…就…;本以为…却…</t>
+          <t>即将…</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ようとする：试图…</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>~ばかりか</t>
+          <t>そこで</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>不仅仅…还…</t>
+          <t>于是…(紧接着做出了某个动作)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -709,45 +717,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>差別</t>
+          <t>～かと思うと</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>歧视；区别对待</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>さべつ</t>
-        </is>
-      </c>
+          <t>刚…就…;本以为…却…</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>~ようとしている</t>
+          <t>~はもとより</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>即将…</t>
+          <t>…自不必说</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>ようとする：试图…</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -755,67 +755,75 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>~限りでは</t>
+          <t>～限り(3)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>根据…</t>
+          <t>(1)尽…(2)仅仅(3)只要…就…</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>かぎ</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>さすが</t>
+          <t>ているところ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>真不愧是</t>
+          <t>正在…</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>原型+ところ-&gt;即将做…    た型+ところ-&gt;刚刚</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>〜からすると</t>
+          <t>~にあたって</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>从…来看</t>
+          <t>当…时候</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>〜からするば</t>
+          <t>接续：辞书形</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>それに</t>
+          <t>~ばかりか</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>此外，再加上</t>
+          <t>不仅仅…还…</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -823,16 +831,16 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>そこで</t>
+          <t>いきなり</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>于是…(紧接着做出了某个动作)</t>
+          <t>突然地</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -840,24 +848,20 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>いつでも</t>
+          <t>~限りでは</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>随时</t>
+          <t>根据…</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>いつまでも-&gt;永远</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -865,12 +869,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>～かなにか</t>
+          <t>~をもとに</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>…之类的</t>
+          <t>以…为基础</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -882,18 +886,18 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>～限り(3)</t>
+          <t>いつでも</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>(1)尽…(2)仅仅(3)只要…就…</t>
+          <t>随时</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>かぎ</t>
+          <t>いつまでも-&gt;永远</t>
         </is>
       </c>
     </row>
@@ -903,20 +907,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ているところ</t>
+          <t>さすが</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>正在…</t>
+          <t>真不愧是</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>原型+ところ-&gt;即将做…    た型+ところ-&gt;刚刚</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -924,50 +924,54 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>~をもとに</t>
+          <t>〜からすると</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>以…为基础</t>
+          <t>从…来看</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>〜からするば</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>門出</t>
+          <t>あふれる</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>开始新生活</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>かどで</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>充满；溢出</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>溢れる</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>~たとたん（に)</t>
+          <t>～おかげで</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>一…就…</t>
+          <t>(1)托…的福(2)都怪</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -975,16 +979,16 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>~に限って</t>
+          <t>～かなにか</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>(1)偏偏…(2)特别坚信</t>
+          <t>…之类的</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -996,15 +1000,19 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>やさしい</t>
+          <t>門出</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>容易的</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>开始新生活</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>かどで</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -1013,16 +1021,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>くせ</t>
+          <t>いじめる</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>毛病；特征</t>
+          <t>欺负</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ほめる-&gt;赞扬，称赞</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1030,12 +1042,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>～おかげで</t>
+          <t>だけ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>(1)托…的福(2)都怪</t>
+          <t>(1)尽可能…(2)仅仅</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1047,16 +1059,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>~からして</t>
+          <t>~ちゃんと</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>即使只抽取一个例子都是这样的，所以整体来看也当然如此</t>
+          <t>牢牢地；好好地</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ちょっと-&gt;稍微；一会儿</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1064,18 +1080,18 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>~てはじめて</t>
+          <t>～か～ないかのうちに</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>只有…，才…</t>
+          <t>刚…就…</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>~をはじめ-&gt;以…为首</t>
+          <t>两处接同一个动词，第一处(原型/た型)，第二处ない形</t>
         </is>
       </c>
     </row>
@@ -1085,12 +1101,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>人びと</t>
+          <t>くせ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>人们</t>
+          <t>毛病；特征</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1102,12 +1118,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>～あいだに</t>
+          <t>~に限って</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>在…期间</t>
+          <t>(1)偏偏…(2)特别坚信</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1119,20 +1135,16 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>~にあたって</t>
+          <t>~たとたん（に)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>当…时候</t>
+          <t>一…就…</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>接续：辞书形</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1140,12 +1152,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ぐらい</t>
+          <t>やさしい</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>(1)程度(2)至少(3)大约</t>
+          <t>容易的</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1153,16 +1165,16 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>お/ご+连用+になる</t>
+          <t>～あいだに</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>尊他语</t>
+          <t>在…期间</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1170,83 +1182,71 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>受け取る</t>
+          <t>~てはじめて</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>领取；理解；承担</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>うけとる</t>
-        </is>
-      </c>
+          <t>只有…，才…</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>受付-&gt;うけつけ</t>
+          <t>~をはじめ-&gt;以…为首</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>~ちゃんと</t>
+          <t>人びと</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>牢牢地；好好地</t>
+          <t>人们</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>ちょっと-&gt;稍微；一会儿</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>回る</t>
+          <t>ぐらい</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>旋转；绕行；巡回</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>まわる</t>
-        </is>
-      </c>
+          <t>(1)程度(2)至少(3)大约</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>だけ</t>
+          <t>~からして</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>(1)尽可能…(2)仅仅</t>
+          <t>即使只抽取一个例子都是这样的，所以整体来看也当然如此</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1258,19 +1258,15 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>来日</t>
+          <t>～をめぐって</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>访日</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>らいにち</t>
-        </is>
-      </c>
+          <t>围绕着…</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
@@ -1279,16 +1275,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>～ているうちに</t>
+          <t>中顿的三种方式</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>在…过程中</t>
+          <t>て、连用、连用+まして</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>“连用”最正式</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1296,20 +1296,16 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>中顿的三种方式</t>
+          <t>～ているうちに</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>て、连用、连用+まして</t>
+          <t>在…过程中</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>“连用”最正式</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1317,15 +1313,19 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>～をめぐって</t>
+          <t>回る</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>围绕着…</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>旋转；绕行；巡回</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>まわる</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -1334,18 +1334,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>～か～ないかのうちに</t>
+          <t>受け取る</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>刚…就…</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>领取；理解；承担</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>うけとる</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>两处接同一个动词，第一处(原型/た型)，第二处ない形</t>
+          <t>受付-&gt;うけつけ</t>
         </is>
       </c>
     </row>
@@ -1355,20 +1359,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ごちそうする</t>
+          <t>来日</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>(我)请客</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>同「おごる」</t>
-        </is>
-      </c>
+          <t>访日</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>らいにち</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1376,20 +1380,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>相次いで</t>
+          <t>ごちそうする</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>相继发生</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>あいつ</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
+          <t>(我)请客</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>同「おごる」</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1397,16 +1401,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>夢中</t>
+          <t>間に</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>着迷；入迷；沉醉</t>
+          <t>后接瞬间动作</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>間 -&gt; 后接持续动作</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1414,20 +1422,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>あふれる</t>
+          <t>相次いで</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>充满；溢出</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>溢れる</t>
-        </is>
-      </c>
+          <t>相继发生</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>あいつ</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1435,20 +1443,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>~うちに + 意志</t>
+          <t>断る(2)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>趁着…</t>
+          <t>提前告知;拒绝</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>~うちに + 不加意志：   在…期间/过程中</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1456,12 +1460,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ごちそうになる</t>
+          <t>お/ご+连用+になる</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>(我)受到款待；被请客</t>
+          <t>尊他语</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -1473,18 +1477,18 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>～次第</t>
+          <t>~うちに + 意志</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>一…就…</t>
+          <t>趁着…</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>N+次第-&gt;取决于…；   次第に-&gt;渐渐…</t>
+          <t>~うちに + 不加意志：   在…期间/过程中</t>
         </is>
       </c>
     </row>
@@ -1494,16 +1498,20 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>断る(2)</t>
+          <t>～次第</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>提前告知;拒绝</t>
+          <t>一…就…</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>N+次第-&gt;取决于…；   次第に-&gt;渐渐…</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1511,20 +1519,16 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>間に</t>
+          <t>ごちそうになる</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>后接瞬间动作</t>
+          <t>(我)受到款待；被请客</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>間 -&gt; 后接持续动作</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1532,12 +1536,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>お+连用+ください</t>
+          <t>ひどい</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>「てください」尊他</t>
+          <t>残酷的；严重的</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -1549,12 +1553,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>そして</t>
+          <t>お+连用+ください</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>而且</t>
+          <t>「てください」尊他</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -1566,12 +1570,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ひどい</t>
+          <t>そして</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>残酷的；严重的</t>
+          <t>而且</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -1583,20 +1587,16 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>いじめる</t>
+          <t>夢中</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>欺负</t>
+          <t>着迷；入迷；沉醉</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>ほめる-&gt;赞扬，称赞</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1604,16 +1604,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>このごろ</t>
+          <t>～上(に)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>最近；近来</t>
+          <t>不仅…而且…</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>～上で(は) -&gt; 在…方面</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1621,12 +1625,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>连用+次第</t>
+          <t>このごろ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>"刚…就…"一般不接人的意志，此处是例外</t>
+          <t>最近；近来</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -1638,12 +1642,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>とおり(2)</t>
+          <t>连用+次第</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>和…一样;按照…</t>
+          <t>"刚…就…"一般不接人的意志，此处是例外</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -1739,20 +1743,16 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>～上(に)</t>
+          <t>でき上がります</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>不仅…而且…</t>
+          <t>完成</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>～上で(は) -&gt; 在…方面</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1760,20 +1760,16 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>～から～にかけて</t>
+          <t>とおり(2)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>从…到…（大致范围）</t>
+          <t>和…一样;按照…</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>～にかけて-&gt;在…方面</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1836,12 +1832,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>でき上がります</t>
+          <t>一类形容词-&gt;名词</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>完成</t>
+          <t>「い」变为「さ」，「い」变为「み」</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -1853,12 +1849,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>一类形容词-&gt;名词</t>
+          <t>しっかりと</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>「い」变为「さ」，「い」变为「み」</t>
+          <t>让“稳稳地、扎实地”这种感觉变得更强调、更正式</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -1870,16 +1866,20 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>しっかりと</t>
+          <t>～から～にかけて</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>让“稳稳地、扎实地”这种感觉变得更强调、更正式</t>
+          <t>从…到…（大致范围）</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>～にかけて-&gt;在…方面</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1949,7 +1949,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1966,16 +1966,16 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>~はさておき</t>
+          <t>してきまる</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>暂且不论；姑且不论</t>
+          <t>做完某事就回来</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -1983,7 +1983,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -2000,16 +2000,16 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ともすると</t>
+          <t>~はさておき</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>容易；往往</t>
+          <t>暂且不论；姑且不论</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -2017,16 +2017,16 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>してきまる</t>
+          <t>ともすると</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>做完某事就回来</t>
+          <t>容易；往往</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -2034,7 +2034,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -2051,33 +2051,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>わがまま</t>
+          <t>～だけある</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>任性；自私</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>真不愧是…</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>常与"さすが"搭配</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>とれる</t>
+          <t>こつこつ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>收获;取得；理解；</t>
+          <t>孜孜不倦；坚持不懈</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -2085,16 +2089,16 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>～だけある</t>
+          <t>～だけのことわある</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>真不愧是…</t>
+          <t>真不愧是...</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2106,37 +2110,33 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>～だけのことわある</t>
+          <t>わがまま</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>真不愧是...</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>常与"さすが"搭配</t>
-        </is>
-      </c>
+          <t>任性；自私</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>寿命</t>
+          <t>とれる</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>じゅみょう</t>
+          <t>收获;取得；理解；</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -2144,16 +2144,16 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>立場</t>
+          <t>いっそう</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>たちば</t>
+          <t>更加</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -2161,16 +2161,16 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>平均</t>
+          <t>~ないことには</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>へいきん</t>
+          <t>如果不…某事就无法实现</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -2178,16 +2178,16 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>普通形+とは</t>
+          <t>せき</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>竟然</t>
+          <t>咳嗽</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -2199,12 +2199,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>せき</t>
+          <t>平均</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>咳嗽</t>
+          <t>へいきん</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -2216,15 +2216,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ｖた＋ところで</t>
+          <t>見舞い</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>即便…</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>慰问；探望；问候</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>みまい</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -2233,12 +2237,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>こつこつ</t>
+          <t>きょうだい</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>孜孜不倦；坚持不懈</t>
+          <t>兄弟姐妹</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -2250,12 +2254,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>〜ずじまいだ</t>
+          <t>何とも言いがたい</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>某事不了了之</t>
+          <t>不知该怎么说</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -2267,12 +2271,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>おば</t>
+          <t>立場</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>姨妈；姑妈；</t>
+          <t>たちば</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -2284,12 +2288,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>~ないことには</t>
+          <t>寿命</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>如果不…某事就无法实现</t>
+          <t>じゅみょう</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -2301,12 +2305,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>いっそう</t>
+          <t>普通形+とは</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>更加</t>
+          <t>竟然</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -2318,12 +2322,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>～ことだし</t>
+          <t>ｖた＋ところで</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>原因</t>
+          <t>即便…</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -2331,37 +2335,33 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>見舞い</t>
+          <t>おば</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>慰问；探望；问候</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>みまい</t>
-        </is>
-      </c>
+          <t>姨妈；姑妈；</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ぼろぼろ</t>
+          <t>〜ずじまいだ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>破烂不堪；破破烂烂</t>
+          <t>某事不了了之</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -2369,16 +2369,16 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>さんざん</t>
+          <t>～ことだし</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>彻底地，拼命地</t>
+          <t>原因</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -2390,12 +2390,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>きょうだい</t>
+          <t>扱う</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>兄弟姐妹</t>
+          <t>处理；对待</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2407,12 +2407,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>~のこととなると</t>
+          <t>さすが</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>一提到…(后续接跟平时不同态度的句子)</t>
+          <t>不愧是…</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2424,12 +2424,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>さすが</t>
+          <t>~のこととなると</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>不愧是…</t>
+          <t>一提到…(后续接跟平时不同态度的句子)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>扱う</t>
+          <t>さんざん</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>处理；对待</t>
+          <t>彻底地，拼命地</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -2458,12 +2458,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>何とも言いがたい</t>
+          <t>ぼろぼろ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>不知该怎么说</t>
+          <t>破烂不堪；破破烂烂</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -2471,16 +2471,16 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>危うい</t>
+          <t>きつい</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>差点…</t>
+          <t>辛苦的；严格；困难；</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -2492,12 +2492,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>今まで</t>
+          <t>~（よ）うものなら</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>以往的</t>
+          <t>如果…的话，后接坏事</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2509,12 +2509,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>连用型+かれる</t>
+          <t>危うい</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>难以…(委婉拒绝)</t>
+          <t>差点…</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -2526,19 +2526,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>～あげく</t>
+          <t>今まで</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>在…之后(令人遗憾的结果)</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>接续是た型</t>
-        </is>
-      </c>
+          <t>以往的</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
@@ -2547,12 +2543,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>～を思いつく</t>
+          <t>连用型+かれる</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>相出(idea)</t>
+          <t>难以…(委婉拒绝)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -2564,15 +2560,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>~（よ）うものなら</t>
+          <t>～あげく</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>如果…的话，后接坏事</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>在…之后(令人遗憾的结果)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>接续是た型</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>きつい</t>
+          <t>～を思いつく</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>辛苦的；严格；困难；</t>
+          <t>相出(idea)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -2598,12 +2598,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>文句の付けようがない</t>
+          <t>たところ、…</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>无可挑剔；完美无缺</t>
+          <t>在…之后</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -2687,12 +2687,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>たところ、…</t>
+          <t>文句の付けようがない</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>在…之后</t>
+          <t>无可挑剔；完美无缺</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -2704,12 +2704,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>面倒を見る</t>
+          <t>5つずつ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>照顾；照料</t>
+          <t>每份五个</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -2721,12 +2721,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>名词+からなる</t>
+          <t>面倒を見る</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>由…构成</t>
+          <t>照顾；照料</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -2738,19 +2738,15 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>て・では</t>
+          <t>名词+からなる</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>假设</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>(1)一类形容词-&gt;くて　(2)二类形容词/名词+で　(3)动词て型</t>
-        </is>
-      </c>
+          <t>由…构成</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
@@ -2759,15 +2755,19 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ありがたい</t>
+          <t>て・では</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>值得感谢的</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>假设</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>(1)一类形容词-&gt;くて　(2)二类形容词/名词+で　(3)动词て型</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -2776,12 +2776,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>パン</t>
+          <t>ありがたい</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>面包</t>
+          <t>值得感谢的</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>~によって(2)</t>
+          <t>パン</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>手段；原因</t>
+          <t>面包</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -2810,12 +2810,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>～わりに</t>
+          <t>~によって(2)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>轻微的转折，后接出乎意料的结果</t>
+          <t>手段；原因</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -2827,12 +2827,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>たとえ悪い結果にしろ</t>
+          <t>～わりに</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>"にしろ"同"でも"</t>
+          <t>轻微的转折，后接出乎意料的结果</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -2844,19 +2844,15 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>N+不足</t>
+          <t>たとえ悪い結果にしろ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ぶそく</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>不足-&gt;ふそく</t>
-        </is>
-      </c>
+          <t>"にしろ"同"でも"</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -2865,12 +2861,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5つずつ</t>
+          <t>ダイヤ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>每份五个</t>
+          <t>列车时刻表；钻石</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -2882,15 +2878,19 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ダイヤ</t>
+          <t>～がする</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>列车时刻表；钻石</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>(第一人称的五官)感到…</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>〜がる-&gt;(第三人称心情)感到…</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -2899,15 +2899,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>~ものか</t>
+          <t>姿勢</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>绝对不…</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>态度；姿态</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>しせい</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
@@ -2916,12 +2920,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>あり得ない</t>
+          <t>~ものか</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>没可能</t>
+          <t>绝对不…</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -2933,12 +2937,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>~わけではない</t>
+          <t>あり得ない</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>部分否定，并非；也不是</t>
+          <t>没可能</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -2950,19 +2954,15 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>连用型+がたい</t>
+          <t>~わけではない</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>难以…(心理活动，而不是能力)</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>たい-&gt;想要</t>
-        </is>
-      </c>
+          <t>部分否定，并非；也不是</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
@@ -2971,15 +2971,19 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ホーム</t>
+          <t>连用型+がたい</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>站台；月台</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>难以…(心理活动，而不是能力)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>たい-&gt;想要</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
@@ -2988,12 +2992,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>普通形+得る・得ない</t>
+          <t>ホーム</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>能够/不能…</t>
+          <t>站台；月台</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -3005,12 +3009,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>~につき</t>
+          <t>普通形+得る・得ない</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>因为…</t>
+          <t>能够/不能…</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -3022,12 +3026,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ｖている＋ところ</t>
+          <t>~につき</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>正在…</t>
+          <t>因为…</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -3039,17 +3043,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>～がする</t>
+          <t>N+不足</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>(第一人称的五官)感到…</t>
+          <t>ぶそく</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>〜がる-&gt;(第三人称心情)感到…</t>
+          <t>不足-&gt;ふそく</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -3060,19 +3064,15 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>姿勢</t>
+          <t>に泊まる</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>态度；姿态</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>しせい</t>
-        </is>
-      </c>
+          <t>临时短住</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>面倒</t>
+          <t>ｖている＋ところ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>麻烦</t>
+          <t>正在…</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -3098,12 +3098,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ラブレター</t>
+          <t>ずに</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>情书</t>
+          <t>ないで正式表达</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ず</t>
+          <t>文句</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ない正式表达</t>
+          <t>抱怨；牢骚</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ひどい</t>
+          <t>ず</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>残酷的；严重的</t>
+          <t>ない正式表达</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -3149,12 +3149,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>～末に</t>
+          <t>ひどい</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>在…之后(做了某个决断)</t>
+          <t>残酷的；严重的</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -3166,12 +3166,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>にもかかわらず</t>
+          <t>～末に</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>尽管；虽然</t>
+          <t>在…之后(做了某个决断)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -3183,12 +3183,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>原型+ところ</t>
+          <t>にもかかわらず</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>即将…</t>
+          <t>尽管；虽然</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -3200,12 +3200,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>及ぶ</t>
+          <t>原型+ところ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>波及，长达</t>
+          <t>即将…</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -3217,12 +3217,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ｖた＋ところ</t>
+          <t>及ぶ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>刚做完…</t>
+          <t>波及，长达</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ずに</t>
+          <t>ｖた＋ところ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ないで正式表达</t>
+          <t>刚做完…</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>文句</t>
+          <t>～もの(结尾)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>抱怨；牢骚</t>
+          <t>原因</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -3268,12 +3268,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>～を思いだす</t>
+          <t>ラブレター</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>想起(旧事)</t>
+          <t>情书</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -3285,12 +3285,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>～もの(结尾)</t>
+          <t>～を思いだす</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>原因</t>
+          <t>想起(旧事)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -3302,12 +3302,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>としか言いようがない</t>
+          <t>面倒</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>只能说是…</t>
+          <t>麻烦</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -3319,12 +3319,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>でも</t>
+          <t>としか言いようがない</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>列举</t>
+          <t>只能说是…</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -3336,12 +3336,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>连用+ようがない</t>
+          <t>でも</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>(1)无法做某事….(2)完全否定</t>
+          <t>列举</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>～わけがない</t>
+          <t>连用+ようがない</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>完全否定</t>
+          <t>(1)无法做某事….(2)完全否定</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -3370,19 +3370,15 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>上昇</t>
+          <t>～わけがない</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>じょうしょう</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>上升；增加</t>
-        </is>
-      </c>
+          <t>完全否定</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
@@ -3391,17 +3387,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>上場</t>
+          <t>上昇</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>じょうじょう</t>
+          <t>じょうしょう</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上升；增加</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -3412,15 +3408,19 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>に泊まる</t>
+          <t>上場</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>临时短住</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>じょうじょう</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr"/>
     </row>
     <row r="86">
@@ -3491,7 +3491,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -3508,24 +3508,28 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>うわさ</t>
+          <t>証拠</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>传闻；流言</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>证据</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>しょうこ</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -3542,7 +3546,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -3563,7 +3567,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -3580,16 +3584,16 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>やはり</t>
+          <t>かゆい</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>果然；毕竟</t>
+          <t>痒</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -3597,37 +3601,33 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>証拠</t>
+          <t>しかる</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>证据</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>しょうこ</t>
-        </is>
-      </c>
+          <t>责备；训斥；斥责</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>かゆい</t>
+          <t>～とみえる</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>痒</t>
+          <t>推测…</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -3635,37 +3635,33 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>口を出す</t>
+          <t>どうにかして</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>插嘴；干预</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>くちをだす</t>
-        </is>
-      </c>
+          <t>想方设法、无论如何</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>しかる</t>
+          <t>うわさ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>责备；训斥；斥责</t>
+          <t>传闻；流言</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -3673,66 +3669,62 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ポリシー</t>
+          <t>に越したことはない</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>政策；方针</t>
+          <t>最好是…</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>policy</t>
+          <t>辞书形</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ささえる</t>
+          <t>やはり</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>支撑；支持</t>
+          <t>果然；毕竟</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>支える</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>に越したことはない</t>
+          <t>口を出す</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>最好是…</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>辞书形</t>
-        </is>
-      </c>
+          <t>插嘴；干预</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>くちをだす</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -3740,12 +3732,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>N+には</t>
+          <t>親戚</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>对象</t>
+          <t>しんせき</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -3757,16 +3749,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>～とみえる</t>
+          <t>ささえる</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>推测…</t>
+          <t>支撑；支持</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>支える</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3774,20 +3770,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>〜ことはない</t>
+          <t>税金</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>没必要做某事</t>
+          <t>ぜいきん</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>辞书形</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3795,12 +3787,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>どうにかして</t>
+          <t>N+には</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>想方设法、无论如何</t>
+          <t>对象</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -3808,37 +3800,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>親戚</t>
+          <t>ポリシー</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>しんせき</t>
+          <t>政策；方针</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>policy</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>気軽に</t>
+          <t>〜ことはない</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>轻松地；随意地</t>
+          <t>没必要做某事</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>辞书形</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3846,15 +3846,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>えさ</t>
+          <t>大切</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>饲料</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>重要</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>たいせつ</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -3863,12 +3867,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>税金</t>
+          <t>～はずだ</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ぜいきん</t>
+          <t>(可能形较高)推测</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -3880,20 +3884,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>~ないわけにはいかない</t>
+          <t>かい</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>(心理上)必须要做某事</t>
+          <t>价值</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>辞书~わけにはいかない-&gt;不能做</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3901,16 +3901,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>〜べきだ</t>
+          <t>~ないではいられない</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>(社会常识或道德性)应该做某事</t>
+          <t>情不自禁做某事</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>主要是第三人称的话，要接"そうだ"</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3918,16 +3922,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>かい</t>
+          <t>~ないわけにはいかない</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>价值</t>
+          <t>(心理上)必须要做某事</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>辞书~わけにはいかない-&gt;不能做</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3935,12 +3943,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>～はずだ</t>
+          <t>えさ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>(可能形较高)推测</t>
+          <t>饲料</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -3952,19 +3960,15 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>大切</t>
+          <t>気軽に</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>重要</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>たいせつ</t>
-        </is>
-      </c>
+          <t>轻松地；随意地</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
@@ -3973,20 +3977,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>~ないではいられない</t>
+          <t>〜べきだ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>情不自禁做某事</t>
+          <t>(社会常识或道德性)应该做某事</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>主要是第三人称的话，要接"そうだ"</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3994,20 +3994,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>〜に相違ない</t>
+          <t>～まい</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>肯定....</t>
+          <t>"ない"的书面语</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>同"に違いない"</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4015,12 +4011,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>主張</t>
+          <t>～にすぎない</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>しゅちょう</t>
+          <t>只不过…</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -4032,16 +4028,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>〜というものだ</t>
+          <t>～かれる</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>从常识开看，简直是…</t>
+          <t>难以…(委婉否定/拒绝)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>接续：连用型</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>出張</t>
+          <t>～ぐらい</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>しゅっちょう</t>
+          <t>(1)最低程度…(2)大约，左右</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -4066,12 +4066,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>とんでもない</t>
+          <t>断る</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>不用;哪里的话</t>
+          <t>事先告知</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -4083,16 +4083,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>～まい</t>
+          <t>〜に相違ない</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>"ない"的书面语</t>
+          <t>肯定....</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>同"に違いない"</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4100,12 +4104,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>断る</t>
+          <t>とんでもない</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>事先告知</t>
+          <t>不用;哪里的话</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -4117,12 +4121,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>～ぐらい</t>
+          <t>出張</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>(1)最低程度…(2)大约，左右</t>
+          <t>しゅっちょう</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -4134,20 +4138,16 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>～かれる</t>
+          <t>〜というものだ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>难以…(委婉否定/拒绝)</t>
+          <t>从常识开看，简直是…</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>接续：连用型</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>～にすぎない</t>
+          <t>主張</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>只不过…</t>
+          <t>しゅちょう</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -4172,20 +4172,16 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>~てしかたがない</t>
+          <t>を的翻译</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>非常…</t>
+          <t>把…</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>主要是第三人称的话，要接"らしい""ようだ"</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4214,15 +4210,19 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>を的翻译</t>
+          <t>引っ張る</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>把…</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t xml:space="preserve">拖拉拽 </t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ひっぱる</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -4231,20 +4231,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>引っ張る</t>
+          <t>~てしかたがない</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">拖拉拽 </t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>ひっぱる</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>非常…</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>主要是第三人称的话，要接"らしい""ようだ"</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4269,20 +4269,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>~ざるを得ない</t>
+          <t>大切にする</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>接续:ない去掉</t>
+          <t>珍惜；爱护</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>特例:する-&gt;せざる</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4290,16 +4286,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>〜にほかならない</t>
+          <t>～さえ～ば・たら・なら</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>正是…</t>
+          <t>只要…就…</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>”さえ”甚至</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>辞书〜ものだ</t>
+          <t>〜ものか</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>(1)真理…(2)最好做…</t>
+          <t>完全否定，口语</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -4324,16 +4324,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>なんて</t>
+          <t>~ずにはいられない</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>竟然；这样的</t>
+          <t>情不自禁做某事</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>主要是第三人称的话，要接"そうだ"</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4341,16 +4345,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>受け入れる</t>
+          <t>~てしょうがない</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>接受</t>
+          <t>非常</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>主要是第三人称的话，要接"らしい""ようだ"</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4358,20 +4366,16 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>~ずにはいられない</t>
+          <t>なんて</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>情不自禁做某事</t>
+          <t>竟然；这样的</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>主要是第三人称的话，要接"そうだ"</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4379,20 +4383,16 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>~てしょうがない</t>
+          <t>辞书〜ものだ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>非常</t>
+          <t>(1)真理…(2)最好做…</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>主要是第三人称的话，要接"らしい""ようだ"</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>〜ものか</t>
+          <t>〜にほかならない</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>完全否定，口语</t>
+          <t>正是…</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -4417,18 +4417,18 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>～さえ～ば・たら・なら</t>
+          <t>~ざるを得ない</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>只要…就…</t>
+          <t>接续:ない去掉</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>”さえ”甚至</t>
+          <t>特例:する-&gt;せざる</t>
         </is>
       </c>
     </row>
@@ -4438,12 +4438,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>大切にする</t>
+          <t>受け入れる</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>珍惜；爱护</t>
+          <t>接受</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>

--- a/Mixed/1_zhouyf.xlsx
+++ b/Mixed/1_zhouyf.xlsx
@@ -480,7 +480,11 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>すくなくも -&gt; 至少</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -488,12 +492,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>名词 + ぎみ</t>
+          <t>めまい</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>稍微有点…的倾向</t>
+          <t>头晕</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -505,12 +509,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>たてもの</t>
+          <t>〜ようにしている</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>建筑物；房屋</t>
+          <t>努力做到…</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -522,12 +526,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>めまい</t>
+          <t>名词 + ぎみ</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>头晕</t>
+          <t>稍微有点…的倾向</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -539,12 +543,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>〜ようにしている</t>
+          <t>たてもの</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>努力做到…</t>
+          <t>建筑物；房屋</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -552,20 +556,24 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ゆうべ</t>
+          <t>~につけて</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>昨晚</t>
+          <t>一…就…；每当…</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>~につれて-&gt;伴随着</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -573,12 +581,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>それに</t>
+          <t>そこで</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>此外，再加上</t>
+          <t>于是…(紧接着做出了某个动作)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -590,15 +598,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>まじめに</t>
+          <t>差別</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>认真；诚实；正经</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>歧视；区别对待</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>さべつ</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -607,33 +619,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>~につけて</t>
+          <t>~ようとしている</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>一…就…；每当…</t>
+          <t>即将…</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>~につれて-&gt;伴随着</t>
+          <t>ようとする：试图…</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>～きる</t>
+          <t>~限りでは</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>把某动作做完</t>
+          <t>根据…</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -641,37 +653,33 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>差別</t>
+          <t>まじめに</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>歧视；区别对待</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>さべつ</t>
-        </is>
-      </c>
+          <t>认真；诚实；正经</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>むかえる</t>
+          <t>それに</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>迎接</t>
+          <t>此外，再加上</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -679,24 +687,20 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>~ようとしている</t>
+          <t>ゆうべ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>即将…</t>
+          <t>昨晚</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>ようとする：试图…</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -704,12 +708,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>そこで</t>
+          <t>~はもとより</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>于是…(紧接着做出了某个动作)</t>
+          <t>…自不必说</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -721,12 +725,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>～かと思うと</t>
+          <t>～きる</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>刚…就…;本以为…却…</t>
+          <t>把某动作做完</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -738,12 +742,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>~はもとより</t>
+          <t>むかえる</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>…自不必说</t>
+          <t>迎接</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -751,24 +755,20 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>～限り(3)</t>
+          <t>～かと思うと</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>(1)尽…(2)仅仅(3)只要…就…</t>
+          <t>刚…就…;本以为…却…</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>かぎ</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -776,20 +776,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ているところ</t>
+          <t>~ばかりか</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>正在…</t>
+          <t>不仅仅…还…</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>原型+ところ-&gt;即将做…    た型+ところ-&gt;刚刚</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -797,20 +793,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>~にあたって</t>
+          <t>いきなり</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>当…时候</t>
+          <t>突然地</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>接续：辞书形</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -818,16 +810,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>~ばかりか</t>
+          <t>ているところ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>不仅仅…还…</t>
+          <t>正在…</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>原型+ところ-&gt;即将做…    た型+ところ-&gt;刚刚</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -835,16 +831,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>いきなり</t>
+          <t>~にあたって</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>突然地</t>
+          <t>当…时候</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>接续：辞书形</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -852,16 +852,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>~限りでは</t>
+          <t>～限り(3)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>根据…</t>
+          <t>(1)尽…(2)仅仅(3)只要…就…</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>かぎ</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -869,16 +873,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>~をもとに</t>
+          <t>あふれる</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>以…为基础</t>
+          <t>充满；溢出</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>溢れる</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -886,20 +894,16 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>いつでも</t>
+          <t>～かなにか</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>随时</t>
+          <t>…之类的</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>いつまでも-&gt;永远</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -907,12 +911,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>さすが</t>
+          <t>～おかげで</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>真不愧是</t>
+          <t>(1)托…的福(2)都怪</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -924,20 +928,16 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>〜からすると</t>
+          <t>~をもとに</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>从…来看</t>
+          <t>以…为基础</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>〜からするば</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -945,18 +945,18 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>あふれる</t>
+          <t>〜からすると</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>充满；溢出</t>
+          <t>从…来看</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>溢れる</t>
+          <t>〜からするば</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>～おかげで</t>
+          <t>さすが</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>(1)托…的福(2)都怪</t>
+          <t>真不愧是</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -983,16 +983,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>～かなにか</t>
+          <t>いつでも</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>…之类的</t>
+          <t>随时</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>いつまでも-&gt;永远</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1000,19 +1004,15 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>門出</t>
+          <t>くせ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>开始新生活</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>かどで</t>
-        </is>
-      </c>
+          <t>毛病；特征</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
@@ -1021,20 +1021,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>いじめる</t>
+          <t>門出</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>欺负</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>ほめる-&gt;赞扬，称赞</t>
-        </is>
-      </c>
+          <t>开始新生活</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>かどで</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1042,16 +1042,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>だけ</t>
+          <t>いじめる</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>(1)尽可能…(2)仅仅</t>
+          <t>欺负</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>ほめる-&gt;赞扬，称赞</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1059,20 +1063,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>~ちゃんと</t>
+          <t>だけ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>牢牢地；好好地</t>
+          <t>(1)尽可能…(2)仅仅</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>ちょっと-&gt;稍微；一会儿</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1080,20 +1080,16 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>～か～ないかのうちに</t>
+          <t>~に限って</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>刚…就…</t>
+          <t>(1)偏偏…(2)特别坚信</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>两处接同一个动词，第一处(原型/た型)，第二处ない形</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1101,16 +1097,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>くせ</t>
+          <t>～か～ないかのうちに</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>毛病；特征</t>
+          <t>刚…就…</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>两处接同一个动词，第一处(原型/た型)，第二处ない形</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1118,16 +1118,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>~に限って</t>
+          <t>~ちゃんと</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>(1)偏偏…(2)特别坚信</t>
+          <t>牢牢地；好好地</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ちょっと-&gt;稍微；一会儿</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1135,12 +1139,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>~たとたん（に)</t>
+          <t>～あいだに</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>一…就…</t>
+          <t>在…期间</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -1152,16 +1156,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>やさしい</t>
+          <t>~てはじめて</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>容易的</t>
+          <t>只有…，才…</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>~をはじめ-&gt;以…为首</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1169,12 +1177,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>～あいだに</t>
+          <t>人びと</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>在…期间</t>
+          <t>人们</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1186,20 +1194,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>~てはじめて</t>
+          <t>ぐらい</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>只有…，才…</t>
+          <t>(1)程度(2)至少(3)大约</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>~をはじめ-&gt;以…为首</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1207,12 +1211,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>人びと</t>
+          <t>~からして</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>人们</t>
+          <t>即使只抽取一个例子都是这样的，所以整体来看也当然如此</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1224,12 +1228,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ぐらい</t>
+          <t>~たとたん（に)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>(1)程度(2)至少(3)大约</t>
+          <t>一…就…</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1241,12 +1245,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>~からして</t>
+          <t>やさしい</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>即使只抽取一个例子都是这样的，所以整体来看也当然如此</t>
+          <t>容易的</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1258,15 +1262,19 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>～をめぐって</t>
+          <t>相次いで</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>围绕着…</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>相继发生</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>あいつ</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
@@ -1275,18 +1283,18 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>中顿的三种方式</t>
+          <t>間に</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>て、连用、连用+まして</t>
+          <t>后接瞬间动作</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>“连用”最正式</t>
+          <t>間 -&gt; 后接持续动作</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1304,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>～ているうちに</t>
+          <t>～をめぐって</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>在…过程中</t>
+          <t>围绕着…</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1313,20 +1321,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>回る</t>
+          <t>中顿的三种方式</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>旋转；绕行；巡回</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>まわる</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
+          <t>て、连用、连用+まして</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>“连用”最正式</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1334,24 +1342,16 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>受け取る</t>
+          <t>～ているうちに</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>领取；理解；承担</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>うけとる</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>受付-&gt;うけつけ</t>
-        </is>
-      </c>
+          <t>在…过程中</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1359,20 +1359,24 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>来日</t>
+          <t>受け取る</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>访日</t>
+          <t>领取；理解；承担</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>らいにち</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
+          <t>うけとる</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>受付-&gt;うけつけ</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1380,20 +1384,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ごちそうする</t>
+          <t>来日</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>(我)请客</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>同「おごる」</t>
-        </is>
-      </c>
+          <t>访日</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>らいにち</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1401,18 +1405,18 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>間に</t>
+          <t>ごちそうする</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>后接瞬间动作</t>
+          <t>(我)请客</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>間 -&gt; 后接持续动作</t>
+          <t>同「おごる」</t>
         </is>
       </c>
     </row>
@@ -1422,17 +1426,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>相次いで</t>
+          <t>回る</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>相继发生</t>
+          <t>旋转；绕行；巡回</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>あいつ</t>
+          <t>まわる</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -1443,12 +1447,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>断る(2)</t>
+          <t>ごちそうになる</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>提前告知;拒绝</t>
+          <t>(我)受到款待；被请客</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -1460,16 +1464,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>お/ご+连用+になる</t>
+          <t>~うちに + 意志</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>尊他语</t>
+          <t>趁着…</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>~うちに + 不加意志：   在…期间/过程中</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1477,18 +1485,18 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>~うちに + 意志</t>
+          <t>～次第</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>趁着…</t>
+          <t>一…就…</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>~うちに + 不加意志：   在…期间/过程中</t>
+          <t>N+次第-&gt;取决于…；   次第に-&gt;渐渐…</t>
         </is>
       </c>
     </row>
@@ -1498,20 +1506,16 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>～次第</t>
+          <t>ひどい</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>一…就…</t>
+          <t>残酷的；严重的</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>N+次第-&gt;取决于…；   次第に-&gt;渐渐…</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1519,12 +1523,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ごちそうになる</t>
+          <t>お+连用+ください</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>(我)受到款待；被请客</t>
+          <t>「てください」尊他</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -1536,12 +1540,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ひどい</t>
+          <t>そして</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>残酷的；严重的</t>
+          <t>而且</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -1553,12 +1557,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>お+连用+ください</t>
+          <t>夢中</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>「てください」尊他</t>
+          <t>着迷；入迷；沉醉</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -1570,12 +1574,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>そして</t>
+          <t>断る(2)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>而且</t>
+          <t>提前告知;拒绝</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -1587,12 +1591,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>夢中</t>
+          <t>お/ご+连用+になる</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>着迷；入迷；沉醉</t>
+          <t>尊他语</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -1604,20 +1608,16 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>～上(に)</t>
+          <t>でき上がります</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>不仅…而且…</t>
+          <t>完成</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>～上で(は) -&gt; 在…方面</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1625,16 +1625,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>このごろ</t>
+          <t>～上(に)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>最近；近来</t>
+          <t>不仅…而且…</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>～上で(は) -&gt; 在…方面</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1642,12 +1646,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>连用+次第</t>
+          <t>このごろ</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>"刚…就…"一般不接人的意志，此处是例外</t>
+          <t>最近；近来</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -1659,24 +1663,16 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>行う</t>
+          <t>连用+次第</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>做…事;举行，实行</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>おこなう</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>行なう</t>
-        </is>
-      </c>
+          <t>"刚…就…"一般不接人的意志，此处是例外</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1743,12 +1739,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>でき上がります</t>
+          <t>一类形容词-&gt;名词</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>完成</t>
+          <t>「い」变为「さ」，「い」变为「み」</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -1760,16 +1756,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>とおり(2)</t>
+          <t>行う</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>和…一样;按照…</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+          <t>做…事;举行，实行</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>おこなう</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>行なう</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1832,12 +1836,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>一类形容词-&gt;名词</t>
+          <t>しっかりと</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>「い」变为「さ」，「い」变为「み」</t>
+          <t>让“稳稳地、扎实地”这种感觉变得更强调、更正式</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -1849,16 +1853,20 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>しっかりと</t>
+          <t>～から～にかけて</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>让“稳稳地、扎实地”这种感觉变得更强调、更正式</t>
+          <t>从…到…（大致范围）</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>～にかけて-&gt;在…方面</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1866,20 +1874,16 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>～から～にかけて</t>
+          <t>とおり(2)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>从…到…（大致范围）</t>
+          <t>和…一样;按照…</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>～にかけて-&gt;在…方面</t>
-        </is>
-      </c>
+      <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1966,16 +1970,16 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>してきまる</t>
+          <t>にあたる</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>做完某事就回来</t>
+          <t>相当于</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -1987,12 +1991,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>にあたる</t>
+          <t>してきまる</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>相当于</t>
+          <t>做完某事就回来</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -2000,7 +2004,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -2051,7 +2055,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -2076,15 +2080,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>こつこつ</t>
+          <t>～だけのことわある</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>孜孜不倦；坚持不懈</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>真不愧是...</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>常与"さすが"搭配</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -2093,19 +2101,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>～だけのことわある</t>
+          <t>わがまま</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>真不愧是...</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>常与"さすが"搭配</t>
-        </is>
-      </c>
+          <t>任性；自私</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -2114,12 +2118,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>わがまま</t>
+          <t>こつこつ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>任性；自私</t>
+          <t>孜孜不倦；坚持不懈</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -2127,16 +2131,16 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>とれる</t>
+          <t>寿命</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>收获;取得；理解；</t>
+          <t>じゅみょう</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -2144,7 +2148,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2161,7 +2165,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2182,12 +2186,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>せき</t>
+          <t>とれる</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>咳嗽</t>
+          <t>收获;取得；理解；</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -2195,16 +2199,16 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>平均</t>
+          <t>せき</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>へいきん</t>
+          <t>咳嗽</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -2216,19 +2220,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>見舞い</t>
+          <t>~のこととなると</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>慰问；探望；问候</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>みまい</t>
-        </is>
-      </c>
+          <t>一提到…(后续接跟平时不同态度的句子)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>きょうだい</t>
+          <t>平均</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>兄弟姐妹</t>
+          <t>へいきん</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -2254,15 +2254,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>何とも言いがたい</t>
+          <t>見舞い</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>不知该怎么说</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>慰问；探望；问候</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>みまい</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -2271,12 +2275,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>立場</t>
+          <t>きょうだい</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>たちば</t>
+          <t>兄弟姐妹</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -2288,12 +2292,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>寿命</t>
+          <t>何とも言いがたい</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>じゅみょう</t>
+          <t>不知该怎么说</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -2305,12 +2309,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>普通形+とは</t>
+          <t>ｖた＋ところで</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>竟然</t>
+          <t>即便…</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -2322,12 +2326,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ｖた＋ところで</t>
+          <t>立場</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>即便…</t>
+          <t>たちば</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -2386,16 +2390,16 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>扱う</t>
+          <t>普通形+とは</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>处理；对待</t>
+          <t>竟然</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2407,12 +2411,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>さすが</t>
+          <t>扱う</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>不愧是…</t>
+          <t>处理；对待</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2424,12 +2428,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>~のこととなると</t>
+          <t>さすが</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>一提到…(后续接跟平时不同态度的句子)</t>
+          <t>不愧是…</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -2492,12 +2496,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>~（よ）うものなら</t>
+          <t>～を思いつく</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>如果…的话，后接坏事</t>
+          <t>相出(idea)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -2509,12 +2513,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>危うい</t>
+          <t>~（よ）うものなら</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>差点…</t>
+          <t>如果…的话，后接坏事</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
@@ -2526,12 +2530,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>今まで</t>
+          <t>危うい</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>以往的</t>
+          <t>差点…</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -2543,12 +2547,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>连用型+かれる</t>
+          <t>今まで</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>难以…(委婉拒绝)</t>
+          <t>以往的</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -2560,19 +2564,15 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>～あげく</t>
+          <t>连用型+かれる</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>在…之后(令人遗憾的结果)</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>接续是た型</t>
-        </is>
-      </c>
+          <t>难以…(委婉拒绝)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -2581,15 +2581,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>～を思いつく</t>
+          <t>～あげく</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>相出(idea)</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>在…之后(令人遗憾的结果)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>接续是た型</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -2598,12 +2602,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>たところ、…</t>
+          <t>文句の付けようがない</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>在…之后</t>
+          <t>无可挑剔；完美无缺</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -2615,12 +2619,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>せずに</t>
+          <t>寝たきり</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>しないで正式表达</t>
+          <t>卧床不起</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -2632,15 +2636,19 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>寝たきり</t>
+          <t>～きり</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>卧床不起</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>做了…后，一直处于某种状态</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>接续是た型</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -2649,19 +2657,15 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>～きり</t>
+          <t>うっかり</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>做了…后，一直处于某种状态</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>接续是た型</t>
-        </is>
-      </c>
+          <t>无意中，差点就</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
@@ -2670,12 +2674,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>うっかり</t>
+          <t>たところ、…</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>无意中，差点就</t>
+          <t>在…之后</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -2687,12 +2691,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>文句の付けようがない</t>
+          <t>せずに</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>无可挑剔；完美无缺</t>
+          <t>しないで正式表达</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -2704,12 +2708,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5つずつ</t>
+          <t>ダイヤ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>每份五个</t>
+          <t>列车时刻表；钻石</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -2721,12 +2725,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>面倒を見る</t>
+          <t>5つずつ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>照顾；照料</t>
+          <t>每份五个</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -2738,12 +2742,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>名词+からなる</t>
+          <t>面倒を見る</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>由…构成</t>
+          <t>照顾；照料</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -2755,19 +2759,15 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>て・では</t>
+          <t>名词+からなる</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>假设</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>(1)一类形容词-&gt;くて　(2)二类形容词/名词+で　(3)动词て型</t>
-        </is>
-      </c>
+          <t>由…构成</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
@@ -2776,15 +2776,19 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ありがたい</t>
+          <t>て・では</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>值得感谢的</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>假设</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>(1)一类形容词-&gt;くて　(2)二类形容词/名词+で　(3)动词て型</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
@@ -2793,12 +2797,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>パン</t>
+          <t>ありがたい</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>面包</t>
+          <t>值得感谢的</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -2810,12 +2814,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>~によって(2)</t>
+          <t>パン</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>手段；原因</t>
+          <t>面包</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -2827,12 +2831,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>～わりに</t>
+          <t>~によって(2)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>轻微的转折，后接出乎意料的结果</t>
+          <t>手段；原因</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -2844,12 +2848,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>たとえ悪い結果にしろ</t>
+          <t>～わりに</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>"にしろ"同"でも"</t>
+          <t>轻微的转折，后接出乎意料的结果</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -2861,15 +2865,19 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ダイヤ</t>
+          <t>～がする</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>列车时刻表；钻石</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>(第一人称的五官)感到…</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>〜がる-&gt;(第三人称心情)感到…</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
@@ -2878,17 +2886,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>～がする</t>
+          <t>N+不足</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>(第一人称的五官)感到…</t>
+          <t>ぶそく</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>〜がる-&gt;(第三人称心情)感到…</t>
+          <t>不足-&gt;ふそく</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2899,19 +2907,15 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>姿勢</t>
+          <t>に泊まる</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>态度；姿态</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>しせい</t>
-        </is>
-      </c>
+          <t>临时短住</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
@@ -2920,15 +2924,19 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>~ものか</t>
+          <t>姿勢</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>绝对不…</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>态度；姿态</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>しせい</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
@@ -2937,12 +2945,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>あり得ない</t>
+          <t>~ものか</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>没可能</t>
+          <t>绝对不…</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -2954,12 +2962,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>~わけではない</t>
+          <t>あり得ない</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>部分否定，并非；也不是</t>
+          <t>没可能</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -2971,19 +2979,15 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>连用型+がたい</t>
+          <t>~わけではない</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>难以…(心理活动，而不是能力)</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>たい-&gt;想要</t>
-        </is>
-      </c>
+          <t>部分否定，并非；也不是</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
@@ -2992,15 +2996,19 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ホーム</t>
+          <t>连用型+がたい</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>站台；月台</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>难以…(心理活动，而不是能力)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>たい-&gt;想要</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
@@ -3009,12 +3017,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>普通形+得る・得ない</t>
+          <t>ホーム</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>能够/不能…</t>
+          <t>站台；月台</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -3026,12 +3034,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>~につき</t>
+          <t>普通形+得る・得ない</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>因为…</t>
+          <t>能够/不能…</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -3043,19 +3051,15 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>N+不足</t>
+          <t>たとえ悪い結果にしろ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ぶそく</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>不足-&gt;ふそく</t>
-        </is>
-      </c>
+          <t>"にしろ"同"でも"</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
@@ -3064,15 +3068,19 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>に泊まる</t>
+          <t>上場</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>临时短住</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>じょうじょう</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
@@ -3081,12 +3089,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ｖている＋ところ</t>
+          <t>~につき</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>正在…</t>
+          <t>因为…</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -3098,12 +3106,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ずに</t>
+          <t>ｖた＋ところ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ないで正式表达</t>
+          <t>刚做完…</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -3115,12 +3123,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>文句</t>
+          <t>～もの(结尾)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>抱怨；牢骚</t>
+          <t>原因</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -3132,12 +3140,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ず</t>
+          <t>文句</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ない正式表达</t>
+          <t>抱怨；牢骚</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -3149,12 +3157,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ひどい</t>
+          <t>ず</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>残酷的；严重的</t>
+          <t>ない正式表达</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -3166,12 +3174,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>～末に</t>
+          <t>ひどい</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>在…之后(做了某个决断)</t>
+          <t>残酷的；严重的</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -3183,12 +3191,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>にもかかわらず</t>
+          <t>～末に</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>尽管；虽然</t>
+          <t>在…之后(做了某个决断)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -3200,12 +3208,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>原型+ところ</t>
+          <t>にもかかわらず</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>即将…</t>
+          <t>尽管；虽然</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -3217,12 +3225,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>及ぶ</t>
+          <t>原型+ところ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>波及，长达</t>
+          <t>即将…</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -3234,12 +3242,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ｖた＋ところ</t>
+          <t>及ぶ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>刚做完…</t>
+          <t>波及，长达</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -3251,12 +3259,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>～もの(结尾)</t>
+          <t>～を思いだす</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>原因</t>
+          <t>想起(旧事)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -3268,12 +3276,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ラブレター</t>
+          <t>ずに</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>情书</t>
+          <t>ないで正式表达</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -3285,12 +3293,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>～を思いだす</t>
+          <t>ラブレター</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>想起(旧事)</t>
+          <t>情书</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -3302,12 +3310,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>面倒</t>
+          <t>ｖている＋ところ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>麻烦</t>
+          <t>正在…</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -3319,12 +3327,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>としか言いようがない</t>
+          <t>面倒</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>只能说是…</t>
+          <t>麻烦</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -3336,12 +3344,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>でも</t>
+          <t>としか言いようがない</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>列举</t>
+          <t>只能说是…</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -3353,12 +3361,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>连用+ようがない</t>
+          <t>でも</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>(1)无法做某事….(2)完全否定</t>
+          <t>列举</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -3370,12 +3378,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>～わけがない</t>
+          <t>连用+ようがない</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>完全否定</t>
+          <t>(1)无法做某事….(2)完全否定</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -3387,19 +3395,15 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>上昇</t>
+          <t>～わけがない</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>じょうしょう</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>上升；增加</t>
-        </is>
-      </c>
+          <t>完全否定</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
@@ -3408,17 +3412,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>上場</t>
+          <t>上昇</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>じょうじょう</t>
+          <t>じょうしょう</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上升；增加</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
@@ -3491,7 +3495,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -3508,7 +3512,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -3529,20 +3533,24 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ぬれる</t>
+          <t>〜にきまっている</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>淋湿；浸湿</t>
+          <t>肯定....</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>〜に決まっている</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -3550,20 +3558,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>〜にきまっている</t>
+          <t>ぬれる</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>肯定....</t>
+          <t>淋湿；浸湿</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>〜に決まっている</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -3673,20 +3677,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>に越したことはない</t>
+          <t>やはり</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>最好是…</t>
+          <t>果然；毕竟</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>辞书形</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -3694,16 +3694,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>やはり</t>
+          <t>に越したことはない</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>果然；毕竟</t>
+          <t>最好是…</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>辞书形</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -3842,41 +3846,41 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>大切</t>
+          <t>えさ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>重要</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>たいせつ</t>
-        </is>
-      </c>
+          <t>饲料</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>～はずだ</t>
+          <t>~ないではいられない</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>(可能形较高)推测</t>
+          <t>情不自禁做某事</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>主要是第三人称的话，要接"そうだ"</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3884,12 +3888,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>かい</t>
+          <t>～まい</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>价值</t>
+          <t>"ない"的书面语</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -3901,20 +3905,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>~ないではいられない</t>
+          <t>～にすぎない</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>情不自禁做某事</t>
+          <t>只不过…</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>主要是第三人称的话，要接"そうだ"</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3922,18 +3922,18 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>~ないわけにはいかない</t>
+          <t>~てしょうがない</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>(心理上)必须要做某事</t>
+          <t>非常</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>辞书~わけにはいかない-&gt;不能做</t>
+          <t>主要是第三人称的话，要接"らしい""ようだ"</t>
         </is>
       </c>
     </row>
@@ -3943,16 +3943,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>えさ</t>
+          <t>~てしかたがない</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>饲料</t>
+          <t>非常…</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>主要是第三人称的话，要接"らしい""ようだ"</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3960,12 +3964,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>気軽に</t>
+          <t>かい</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>轻松地；随意地</t>
+          <t>价值</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -3977,46 +3981,54 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>〜べきだ</t>
+          <t>大切</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>(社会常识或道德性)应该做某事</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>重要</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>たいせつ</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>～まい</t>
+          <t>~ないわけにはいかない</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>"ない"的书面语</t>
+          <t>(心理上)必须要做某事</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>辞书~わけにはいかない-&gt;不能做</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>～にすぎない</t>
+          <t>気軽に</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>只不过…</t>
+          <t>轻松地；随意地</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -4024,37 +4036,33 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>～かれる</t>
+          <t>〜べきだ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>难以…(委婉否定/拒绝)</t>
+          <t>(社会常识或道德性)应该做某事</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>接续：连用型</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>～ぐらい</t>
+          <t>～はずだ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>(1)最低程度…(2)大约，左右</t>
+          <t>(可能形较高)推测</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -4066,12 +4074,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>断る</t>
+          <t>を的翻译</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>事先告知</t>
+          <t>把…</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -4083,18 +4091,18 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>〜に相違ない</t>
+          <t>～かれる</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>肯定....</t>
+          <t>难以…(委婉否定/拒绝)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>同"に違いない"</t>
+          <t>接续：连用型</t>
         </is>
       </c>
     </row>
@@ -4104,12 +4112,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>とんでもない</t>
+          <t>～ぐらい</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>不用;哪里的话</t>
+          <t>(1)最低程度…(2)大约，左右</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -4121,12 +4129,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>出張</t>
+          <t>断る</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>しゅっちょう</t>
+          <t>事先告知</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -4138,16 +4146,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>〜というものだ</t>
+          <t>〜に相違ない</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>从常识开看，简直是…</t>
+          <t>肯定....</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>同"に違いない"</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4155,12 +4167,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>主張</t>
+          <t>とんでもない</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>しゅちょう</t>
+          <t>不用;哪里的话</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -4172,12 +4184,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>を的翻译</t>
+          <t>出張</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>把…</t>
+          <t>しゅっちょう</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -4189,20 +4201,16 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>～かれない</t>
+          <t>〜というものだ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>很可能…(坏结果)</t>
+          <t>从常识开看，简直是…</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>接续：连用型</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4210,19 +4218,15 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>引っ張る</t>
+          <t>主張</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">拖拉拽 </t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>ひっぱる</t>
-        </is>
-      </c>
+          <t>しゅちょう</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
@@ -4231,18 +4235,18 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>~てしかたがない</t>
+          <t>～かれない</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>非常…</t>
+          <t>很可能…(坏结果)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>主要是第三人称的话，要接"らしい""ようだ"</t>
+          <t>接续：连用型</t>
         </is>
       </c>
     </row>
@@ -4252,15 +4256,19 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>〜など</t>
+          <t>引っ張る</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>诸如此类不重要的东西</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t xml:space="preserve">拖拉拽 </t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ひっぱる</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
@@ -4269,12 +4277,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>大切にする</t>
+          <t>〜など</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>珍惜；爱护</t>
+          <t>诸如此类不重要的东西</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -4286,20 +4294,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>～さえ～ば・たら・なら</t>
+          <t>大切にする</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>只要…就…</t>
+          <t>珍惜；爱护</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>”さえ”甚至</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4307,16 +4311,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>〜ものか</t>
+          <t>～さえ～ば・たら・なら</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>完全否定，口语</t>
+          <t>只要…就…</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>”さえ”甚至</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4324,20 +4332,16 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>~ずにはいられない</t>
+          <t>〜ものか</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>情不自禁做某事</t>
+          <t>完全否定，口语</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>主要是第三人称的话，要接"そうだ"</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4345,18 +4349,18 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>~てしょうがない</t>
+          <t>~ずにはいられない</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>非常</t>
+          <t>情不自禁做某事</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>主要是第三人称的话，要接"らしい""ようだ"</t>
+          <t>主要是第三人称的话，要接"そうだ"</t>
         </is>
       </c>
     </row>
